--- a/naver-place-crawler/results_health/판교_헬스장.xlsx
+++ b/naver-place-crawler/results_health/판교_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,24 +596,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wi2wapb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2525</v>
+        <v>2535</v>
       </c>
       <c r="Q2" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="R2" t="n">
-        <v>2844</v>
+        <v>2857</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>스포짐 판교역점</t>
+          <t>스포짐 판교점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>showmethecash@naver.com</t>
+          <t>spogym_2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1436-1236</t>
+          <t>0507-1476-8384</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 117 B101호</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/spogym_pg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w444pd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1244</v>
+        <v>732</v>
       </c>
       <c r="Q3" t="n">
-        <v>638</v>
+        <v>624</v>
       </c>
       <c r="R3" t="n">
-        <v>1882</v>
+        <v>1356</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1088507385</t>
+          <t>20123697</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088507385</t>
+          <t>https://m.place.naver.com/place/20123697</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>헤일로짐24시 헬스 PT 판교점</t>
+          <t>스포짐 판교역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>halogym02@naver.com</t>
+          <t>showmethecash@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1315-8840</t>
+          <t>0507-1436-1236</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+          <t>경기도 성남시 분당구 분당내곡로 117 B101호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/spogym_p.g/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -802,32 +794,28 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcfevb4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>662</v>
+        <v>1247</v>
       </c>
       <c r="Q4" t="n">
-        <v>913</v>
+        <v>641</v>
       </c>
       <c r="R4" t="n">
-        <v>1575</v>
+        <v>1888</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1806695299</t>
+          <t>1088507385</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806695299</t>
+          <t>https://m.place.naver.com/place/1088507385</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -904,14 +892,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42raj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>O</t>
@@ -923,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1758</v>
+        <v>1766</v>
       </c>
       <c r="Q5" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="R5" t="n">
-        <v>2002</v>
+        <v>2015</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -948,7 +932,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -960,34 +944,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포짐 판교점</t>
+          <t>헤일로짐24시 헬스 PT 판교점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>spogym7@naver.com</t>
+          <t>halogym02@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1476-8384</t>
+          <t>0507-1315-8840</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://booking.naver.com/booking/6/bizes/933331</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -997,37 +981,33 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wpasubw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>728</v>
+        <v>663</v>
       </c>
       <c r="Q6" t="n">
-        <v>587</v>
+        <v>925</v>
       </c>
       <c r="R6" t="n">
-        <v>1315</v>
+        <v>1588</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1036,17 +1016,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>20123697</t>
+          <t>1806695299</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20123697</t>
+          <t>https://m.place.naver.com/place/1806695299</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1060,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/9s_gym_pangyo/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1090,7 +1070,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1100,14 +1080,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wyuehl2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1122,10 +1098,10 @@
         <v>161</v>
       </c>
       <c r="Q7" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="R7" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1144,7 +1120,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1156,59 +1132,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>쿼드짐</t>
+          <t>버핏그라운드 PT 판교</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>quadgym@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1303-9415</t>
+          <t>0507-1417-1133</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc5w2o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1217,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1232,17 +1208,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1759307500</t>
+          <t>2029680813</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759307500</t>
+          <t>https://m.place.naver.com/place/2029680813</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1254,29 +1230,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>베스트바디발란스</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wjdwktnso@naver.com</t>
+          <t>humblefitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1402-7136</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1286,24 +1262,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc9u20</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1311,17 +1283,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="Q9" t="n">
-        <v>107</v>
+        <v>1437</v>
       </c>
       <c r="R9" t="n">
-        <v>161</v>
+        <v>1579</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1330,17 +1302,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>36428321</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36428321</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1352,25 +1324,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>렛미PT&amp;필라테스스튜디오 분당야탑점</t>
+          <t>더바디짐 PT 분당수내점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>let_me_pt_official@naver.com</t>
+          <t>thebodyptgym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1387-7676</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 21 영진다이비스상가 2층 210호</t>
+          <t>경기도 성남시 분당구 수내로46번길 11 대덕글로리빌딩 5층 더바디짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/thebodyptgym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,24 +1356,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42m9n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1409,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="Q10" t="n">
-        <v>49</v>
+        <v>1711</v>
       </c>
       <c r="R10" t="n">
-        <v>128</v>
+        <v>1864</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,115 +1396,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1049956503</t>
+          <t>36666737</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049956503</t>
+          <t>https://m.place.naver.com/place/36666737</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>H GYM PT GT 판교2호점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>hgym9408@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1353-9408</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 운중로 233 302호</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://hgym.imweb.me</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47alh</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>278</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>418</v>
-      </c>
-      <c r="R11" t="n">
-        <v>696</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1850894755</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1850894755</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/판교_헬스장.xlsx
+++ b/naver-place-crawler/results_health/판교_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>클럽 브릭스 판교</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>club_breex@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>031-625-5566</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 분당내곡로 131 판교테크원타워 B1 클럽브릭스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>https://blog.naver.com/club_breex</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2535</v>
+        <v>331</v>
       </c>
       <c r="Q2" t="n">
-        <v>322</v>
+        <v>94</v>
       </c>
       <c r="R2" t="n">
-        <v>2857</v>
+        <v>425</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1141858723</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1141858723</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>spogym_2@naver.com</t>
+          <t>spogym7@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spogym_pg</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -700,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wpasubw</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="Q3" t="n">
         <v>624</v>
       </c>
       <c r="R3" t="n">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,41 +744,41 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>스포짐 판교역점</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>showmethecash@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1436-1236</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 117 B101호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spogym_p.g/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +788,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -794,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1247</v>
+        <v>2540</v>
       </c>
       <c r="Q4" t="n">
-        <v>641</v>
+        <v>323</v>
       </c>
       <c r="R4" t="n">
-        <v>1888</v>
+        <v>2863</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1088507385</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088507385</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -892,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42raj</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>O</t>
@@ -907,10 +919,10 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="Q5" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="R5" t="n">
         <v>2015</v>
@@ -932,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -944,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헤일로짐24시 헬스 PT 판교점</t>
+          <t>스포짐 판교역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>halogym02@naver.com</t>
+          <t>showmethecash@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1315-8840</t>
+          <t>0507-1436-1236</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+          <t>경기도 성남시 분당구 분당내곡로 117 B101호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/933331</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -981,33 +993,37 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w444pd</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>663</v>
+        <v>1251</v>
       </c>
       <c r="Q6" t="n">
-        <v>925</v>
+        <v>642</v>
       </c>
       <c r="R6" t="n">
-        <v>1588</v>
+        <v>1893</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,51 +1032,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1806695299</t>
+          <t>1088507385</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806695299</t>
+          <t>https://m.place.naver.com/place/1088507385</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>헤일로짐24시 헬스 PT 판교점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
+          <t>halogym02@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>0507-1315-8840</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1070,7 +1086,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1080,28 +1096,32 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfevb4</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>161</v>
+        <v>663</v>
       </c>
       <c r="Q7" t="n">
-        <v>143</v>
+        <v>927</v>
       </c>
       <c r="R7" t="n">
-        <v>304</v>
+        <v>1590</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,70 +1130,62 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>1806695299</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/1806695299</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 판교</t>
+          <t>팀버핏 판교</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1417-1133</t>
-        </is>
-      </c>
+          <t>teambutfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하3층 B3008</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1184,7 +1196,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1193,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,17 +1220,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2029680813</t>
+          <t>1004612269</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029680813</t>
+          <t>https://m.place.naver.com/place/1004612269</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1230,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>구스짐 PT 판교점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
+          <t>chlgudrn1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1465-9683</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1262,20 +1274,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyuehl2</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1287,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="Q9" t="n">
-        <v>1437</v>
+        <v>143</v>
       </c>
       <c r="R9" t="n">
-        <v>1579</v>
+        <v>305</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>1088776551</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/1088776551</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1324,29 +1340,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더바디짐 PT 분당수내점</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>thebodyptgym@naver.com</t>
+          <t>humblefitness@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1387-7676</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로46번길 11 대덕글로리빌딩 5층 더바디짐</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thebodyptgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1356,20 +1372,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wnvkt3b</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1381,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="Q10" t="n">
-        <v>1711</v>
+        <v>1437</v>
       </c>
       <c r="R10" t="n">
-        <v>1864</v>
+        <v>1578</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,17 +1416,115 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>36666737</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36666737</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>버핏그라운드 PT 판교</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1417-1133</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.butfitground.com/4steppt</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2029680813</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2029680813</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/판교_헬스장.xlsx
+++ b/naver-place-crawler/results_health/판교_헬스장.xlsx
@@ -426,8 +426,8 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>클럽 브릭스 판교</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>club_breex@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>031-625-5566</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 131 판교테크원타워 B1 클럽브릭스</t>
+          <t>경기 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/club_breex</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>331</v>
+        <v>2540</v>
       </c>
       <c r="Q2" t="n">
-        <v>94</v>
+        <v>323</v>
       </c>
       <c r="R2" t="n">
-        <v>425</v>
+        <v>2863</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1141858723</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1141858723</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -663,7 +667,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>spogym7@naver.com</t>
+          <t>spogym_2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -675,12 +679,12 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
+          <t>경기 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/spogym_pg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -751,34 +755,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,12 +796,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -803,12 +811,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wi2wapb</t>
+          <t>https://talk.naver.com/ct/w42raj</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -817,13 +825,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2540</v>
+        <v>1765</v>
       </c>
       <c r="Q4" t="n">
-        <v>323</v>
+        <v>250</v>
       </c>
       <c r="R4" t="n">
-        <v>2863</v>
+        <v>2015</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +840,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,33 +862,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>스포짐 판교역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>showmethecash@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1436-1236</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기 성남시 분당구 분당내곡로 117 B101호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://www.instagram.com/spogym_p.g/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +899,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,12 +909,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42raj</t>
+          <t>https://talk.naver.com/ct/w444pd</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +923,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1765</v>
+        <v>1251</v>
       </c>
       <c r="Q5" t="n">
-        <v>250</v>
+        <v>642</v>
       </c>
       <c r="R5" t="n">
-        <v>2015</v>
+        <v>1893</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +938,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1088507385</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1088507385</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,34 +960,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포짐 판교역점</t>
+          <t>헤일로짐24시 헬스 PT 판교점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>showmethecash@naver.com</t>
+          <t>halogym02@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1436-1236</t>
+          <t>0507-1315-8840</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 117 B101호</t>
+          <t>경기 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://booking.naver.com/booking/6/bizes/933331</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -993,7 +997,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,27 +1007,27 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w444pd</t>
+          <t>https://talk.naver.com/ct/wcfevb4</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1251</v>
+        <v>663</v>
       </c>
       <c r="Q6" t="n">
-        <v>642</v>
+        <v>927</v>
       </c>
       <c r="R6" t="n">
-        <v>1893</v>
+        <v>1590</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1036,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1088507385</t>
+          <t>1806695299</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088507385</t>
+          <t>https://m.place.naver.com/place/1806695299</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1058,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헤일로짐24시 헬스 PT 판교점</t>
+          <t>원팀짐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>halogym02@naver.com</t>
+          <t>oneteamgym-@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1315-8840</t>
+          <t>031-702-2070</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+          <t>경기 성남시 분당구 운중로 128 7층 701호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/oneteamgym1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,7 +1090,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1101,27 +1105,27 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcfevb4</t>
+          <t>https://talk.naver.com/ct/wl0ubx8</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>663</v>
+        <v>492</v>
       </c>
       <c r="Q7" t="n">
-        <v>927</v>
+        <v>289</v>
       </c>
       <c r="R7" t="n">
-        <v>1590</v>
+        <v>781</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1134,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1806695299</t>
+          <t>1973455447</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806695299</t>
+          <t>https://m.place.naver.com/place/1973455447</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,40 +1156,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>팀버핏 판교</t>
+          <t>투엑스휘트니스 분당점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>teambutfit@naver.com</t>
+          <t>2xfit@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>031-782-5115</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하3층 B3008</t>
+          <t>경기 성남시 분당구 정자일로 177 분당인텔리지2 3F</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.2xfitness.co.kr/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1205,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>236</v>
+        <v>431</v>
       </c>
       <c r="Q8" t="n">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="R8" t="n">
-        <v>331</v>
+        <v>459</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1004612269</t>
+          <t>32278618</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1004612269</t>
+          <t>https://m.place.naver.com/place/32278618</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1259,12 +1267,12 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기 성남시 분당구 판교로 374 스타식스코아2 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/9s_gym_pangyo/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1274,7 +1282,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1303,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q9" t="n">
         <v>143</v>
       </c>
       <c r="R9" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1357,12 +1365,12 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1372,12 +1380,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1438,38 +1446,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 판교</t>
+          <t>베스트바디발란스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>wjdwktnso@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1417-1133</t>
+          <t>0507-1402-7136</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+          <t>경기 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://blog.naver.com/wjdwktnso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1484,28 +1488,32 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc9u20</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2029680813</t>
+          <t>36428321</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029680813</t>
+          <t>https://m.place.naver.com/place/36428321</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/판교_헬스장.xlsx
+++ b/naver-place-crawler/results_health/판교_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>그라운드피트니스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>ground-fitness@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1464-5758</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 서현로 170 풍림아이원플러스 3층 301호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>https://blog.naver.com/ground-fitness</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wi2wapb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2540</v>
+        <v>374</v>
       </c>
       <c r="Q2" t="n">
-        <v>323</v>
+        <v>1211</v>
       </c>
       <c r="R2" t="n">
-        <v>2863</v>
+        <v>1585</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1472483345</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1472483345</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>스포짐 판교점</t>
+          <t>레조나헬스랩PT 서판교점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>spogym_2@naver.com</t>
+          <t>resonar_healthlab@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1476-8384</t>
+          <t>0507-1411-1104</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
+          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spogym_pg</t>
+          <t>https://blog.naver.com/resonar_healthlab</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,19 +695,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wpasubw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>731</v>
+        <v>56</v>
       </c>
       <c r="Q3" t="n">
-        <v>624</v>
+        <v>202</v>
       </c>
       <c r="R3" t="n">
-        <v>1355</v>
+        <v>258</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>20123697</t>
+          <t>1644348689</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20123697</t>
+          <t>https://m.place.naver.com/place/1644348689</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,38 +747,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>하이퀄짐 헬스PT 판교점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>highqualgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1364-9601</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 운중로 128 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://www.instagram.com/highqualgym2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -801,22 +789,18 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42raj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -825,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1765</v>
+        <v>58</v>
       </c>
       <c r="Q4" t="n">
-        <v>250</v>
+        <v>103</v>
       </c>
       <c r="R4" t="n">
-        <v>2015</v>
+        <v>161</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -840,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1012638231</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1012638231</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -862,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>스포짐 판교역점</t>
+          <t>밥스짐 분당점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>showmethecash@naver.com</t>
+          <t>ish0674@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1436-1236</t>
+          <t>0507-1474-7017</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 분당내곡로 117 B101호</t>
+          <t>경기도 성남시 분당구 성남대로 449 로얄팰리스 에이동 212, 213, 214호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spogym_p.g/</t>
+          <t>https://www.instagram.com/bobsgymbob/profilecard/?igsh=MTFxcDRvanRsZ2ZyNA==</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -904,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w444pd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -923,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1251</v>
+        <v>82</v>
       </c>
       <c r="Q5" t="n">
-        <v>642</v>
+        <v>185</v>
       </c>
       <c r="R5" t="n">
-        <v>1893</v>
+        <v>267</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -938,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1088507385</t>
+          <t>1581057750</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088507385</t>
+          <t>https://m.place.naver.com/place/1581057750</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -960,34 +940,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헤일로짐24시 헬스 PT 판교점</t>
+          <t>봇들마을8단지한신휴플러스아파트휘트니스센터</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>halogym02@naver.com</t>
+          <t>1logdesign@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1315-8840</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+          <t>경기도 성남시 분당구 동판교로 153</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/933331</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -997,22 +973,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcfevb4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1021,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>663</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>927</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1590</v>
+        <v>1</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1036,12 +1008,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1806695299</t>
+          <t>1443133117</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806695299</t>
+          <t>https://m.place.naver.com/place/1443133117</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1053,34 +1025,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>원팀짐</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>oneteamgym-@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>031-702-2070</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 운중로 128 7층 701호</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oneteamgym1</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1095,19 +1067,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wl0ubx8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1119,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>492</v>
+        <v>2540</v>
       </c>
       <c r="Q7" t="n">
-        <v>289</v>
+        <v>323</v>
       </c>
       <c r="R7" t="n">
-        <v>781</v>
+        <v>2863</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1134,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1973455447</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973455447</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1156,34 +1124,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>투엑스휘트니스 분당점</t>
+          <t>엔엘휘트니스 분당이매점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2xfit@naver.com</t>
+          <t>nlfitness2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-782-5115</t>
+          <t>0507-1415-2075</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 정자일로 177 분당인텔리지2 3F</t>
+          <t>경기도 성남시 분당구 판교로 440 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.2xfitness.co.kr/</t>
+          <t>https://www.instagram.com/nlfitness2_imae/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1193,7 +1161,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1213,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>431</v>
+        <v>642</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>241</v>
       </c>
       <c r="R8" t="n">
-        <v>459</v>
+        <v>883</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>32278618</t>
+          <t>1194690742</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32278618</t>
+          <t>https://m.place.naver.com/place/1194690742</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>헬스보이짐&amp;필라걸 수내점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
+          <t>healthboy40@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>0507-1380-2239</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 내정로173번길 49 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+          <t>https://blog.naver.com/healthboy40/223688037867</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,19 +1255,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wyuehl2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1311,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>163</v>
+        <v>968</v>
       </c>
       <c r="Q9" t="n">
-        <v>143</v>
+        <v>734</v>
       </c>
       <c r="R9" t="n">
-        <v>306</v>
+        <v>1702</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>1973151166</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/1973151166</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,44 +1307,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>헤일로짐24시 헬스 PT 판교점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
+          <t>halogym02@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>031-697-8768</t>
+          <t>0507-1315-8840</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>https://booking.naver.com/booking/6/bizes/933331</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1390,32 +1354,28 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wnvkt3b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>141</v>
+        <v>663</v>
       </c>
       <c r="Q10" t="n">
-        <v>1437</v>
+        <v>929</v>
       </c>
       <c r="R10" t="n">
-        <v>1578</v>
+        <v>1592</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>1806695299</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/1806695299</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1441,39 +1401,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>베스트바디발란스</t>
+          <t>커스텀핏 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wjdwktnso@naver.com</t>
+          <t>customfitpt@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1402-7136</t>
+          <t>031-8016-5677</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
+          <t>경기도 성남시 분당구 운중로 123 마크시티 오렌지동 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjdwktnso</t>
+          <t>https://booking.naver.com/https://booking.naver.com/booking/5/bizes/795160/items/4714422?preview=1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1483,19 +1443,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc9u20</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1507,30 +1463,6140 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>35644006</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35644006</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>바디센서리 판교점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bodysensory@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1344-2096</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 41 프라임스퀘어 10층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/BumGi</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>292</v>
+      </c>
+      <c r="R12" t="n">
+        <v>338</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1786901360</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1786901360</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>버핏그라운드 판교벤처타운</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1315-3624</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로644번길 49 B2층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.butfitground.com/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>29</v>
+      </c>
+      <c r="R13" t="n">
+        <v>140</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2064425838</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2064425838</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>런던피트니스&amp;필라테스 분당이매점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>londoner83@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1406-9679</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/londoner83</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1340</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>473</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1813</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>13530251</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13530251</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>익스홀릭 가넷 이매점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>exholicimae@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1450-3374</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 이매로 45 이수프라자</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/exholicimae</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>310</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>228</v>
+      </c>
+      <c r="R15" t="n">
+        <v>538</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>21281338</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21281338</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>스포애니 서현역점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>spoany22@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>031-706-8522</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로 324 좋은상호저축은행빌딩 B1층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany22</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>950</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2036</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2986</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>13025013</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13025013</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>팀버핏 판교</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하3층 B3008</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/butfitground</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>95</v>
+      </c>
+      <c r="R17" t="n">
+        <v>331</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1004612269</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1004612269</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>블랙스미스짐 헬스PT 판교점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>emmaholic1@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1352-4388</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 지하2층 비2147호, 비2148호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>http://blacksmithgym.kr/</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
         <v>107</v>
       </c>
-      <c r="R11" t="n">
-        <v>161</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>36428321</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/36428321</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="Q18" t="n">
+        <v>194</v>
+      </c>
+      <c r="R18" t="n">
+        <v>301</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1462760829</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1462760829</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>F45 판교</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ksh1992001@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>pangyo.admin@f45training.kr</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하 1층 119-6호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>http://www.f45training.kr/pangyo</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>105</v>
+      </c>
+      <c r="R19" t="n">
+        <v>208</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1017940051</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1017940051</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>스포짐 판교역점</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>showmethecash@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1436-1236</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 분당내곡로 117 B101호</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/spogym_p.g/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>1252</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>641</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1893</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1088507385</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1088507385</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PDC스포츠센터</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>spxkzjs12@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>031-8060-0377</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 242 판교디지털센터 A동 2층 PDC스포츠센터</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>19</v>
+      </c>
+      <c r="R21" t="n">
+        <v>71</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1057141943</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1057141943</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>짐라이언피트니스 수내역1호점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>liongym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1319-1102</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 수내로46번길 11 지하1층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gymlion_sunae</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>1701</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>343</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2044</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1628575924</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1628575924</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>클럽 브릭스 판교</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>club_breex@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>031-625-5566</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 분당내곡로 131 판교테크원타워 B1 클럽브릭스</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/club_breex</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>331</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>94</v>
+      </c>
+      <c r="R23" t="n">
+        <v>425</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1141858723</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1141858723</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>산운휘트니스센타</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>gusdk021@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1405-9688</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교원로 68</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>20123481</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20123481</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>피트니스패밀리</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>tkdkrkwl@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>031-739-7188</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로712번길 22</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>30817753</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/30817753</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>헬스플러스 판교5호점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>healthplus_pangyo5@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1313-1507</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로2길 2 지하1층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/healthplus_pangyo5/</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>674</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1070</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1744</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1086359388</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1086359388</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>휘트니스클럽S 이매점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>fitnessclubs10@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1442-7786</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 446 그린프라자 3층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitnessclubs10</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>525</v>
+      </c>
+      <c r="R27" t="n">
+        <v>724</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>38673070</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38673070</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>고릴라멀티짐 분당서현점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>gorillagym6@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1373-0880</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로 192 야베스벨리 5층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gorillamultigym_bundangseohyun?igsh=cWMyMDFqYjZsdjg5&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>652</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>949</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1601</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>31457116</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31457116</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>버핏그라운드 판교</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1329-4325</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://pt.butfitground.com/</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>1765</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>250</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2015</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1136752576</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1136752576</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>F45 서현</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>yerim1118@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>031-702-4520</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로342번길 21 대정빌딩 지하 1층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/f45_seohyeon/</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>468</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>96</v>
+      </c>
+      <c r="R30" t="n">
+        <v>564</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1316630678</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1316630678</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>원팀짐</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>oneteamgym-@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>031-702-2070</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 128 7층 701호</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oneteamgym1</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>492</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>289</v>
+      </c>
+      <c r="R31" t="n">
+        <v>781</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1973455447</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1973455447</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>크로스핏 라운지</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>crossfit_lounge@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1321-6851</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로319번길 8-4 지하1층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/crossfit_lounge</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>271</v>
+      </c>
+      <c r="R32" t="n">
+        <v>314</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2067270233</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2067270233</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>파크뷰휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>parkviewf1004@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>parkview.f.1004@gmail.com</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>031-783-3000</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로 248 파크뷰상가 3층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.parkviewfc.co.kr</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>127</v>
+      </c>
+      <c r="R33" t="n">
+        <v>175</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>11847077</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11847077</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>운동공간픽스앤빌드</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>physio_congmi@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1433-4667</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 산운로160번길 10 1층 101호</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.themosttimes.co.kr/39064</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>430</v>
+      </c>
+      <c r="R34" t="n">
+        <v>494</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1637759423</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1637759423</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>스포짐 판교점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>spogym_2@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1476-8384</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/spogym_pg</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>731</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>624</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1355</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>20123697</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20123697</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>업투휘트니스 분당삼평점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>upto_sampyeong@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1466-1103</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 375 4층 401-2,402~405호</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/upto_sampyeong</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>562</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>555</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1117</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1878300058</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1878300058</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>트랜스핏짐 서현역점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>transfit_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1387-9682</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 분당로53번길 15 지하1층 트랜스핏짐 서현역점</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/transfit_gym</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>2191</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2247</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4438</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1487183442</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1487183442</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>스타디온 판교 크로스핏</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sbkim10@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>031-603-1109</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로177번길 25 지하B103호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stadion_pangyo_crossfit?igsh=MXg2azI4ZjFsemtkMw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>326</v>
+      </c>
+      <c r="R38" t="n">
+        <v>440</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1332230479</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1332230479</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>버핏그라운드 PT 판교</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1417-1133</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.butfitground.com/4steppt</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2029680813</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2029680813</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H GYM PT GT 판교2호점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>hgym9408@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1353-9408</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://hgym.imweb.me</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>279</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>419</v>
+      </c>
+      <c r="R40" t="n">
+        <v>698</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1850894755</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1850894755</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>피티스튜디오이룸 PT EROOM</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ptstudioeroom@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1361-7934</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 45 3층 303호</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ptstudioeroom</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>32</v>
+      </c>
+      <c r="R41" t="n">
+        <v>78</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1164280530</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1164280530</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>핏앤클래시 PT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>fitclassy22@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1325-5251</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서판교로 154 낙생빌딩 201호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitclassy22</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>22</v>
+      </c>
+      <c r="R42" t="n">
+        <v>65</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1283224823</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1283224823</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>에너지플로우짐</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>exerscience@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1346-9129</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 230 B동 지하1층 B126-1호</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://energyflowlab.my.canva.site</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>38</v>
+      </c>
+      <c r="R43" t="n">
+        <v>39</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1846760075</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1846760075</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>여성전용 비조 필라PT 자이로토닉</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>viyulgallery@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 132</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.themosttimes.co.kr/43811</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>50</v>
+      </c>
+      <c r="R44" t="n">
+        <v>179</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1600591794</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1600591794</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>엑서사이언스짐</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>exerscience@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 240 삼환하이펙스A동 B1층 B117-1호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>143</v>
+      </c>
+      <c r="R45" t="n">
+        <v>150</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1746641680</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1746641680</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>린바디핏 PT 판교본점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>leanbodyfitv2@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1302-8312</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로 670 지하113호</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/leanbodyfitv2</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>108</v>
+      </c>
+      <c r="R46" t="n">
+        <v>243</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1699238533</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1699238533</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>피티세븐 퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>body2balance@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1400-9428</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로132번길 22-1 1층 102호 피티세븐</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>http://www.pts7.com</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>302</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>291</v>
+      </c>
+      <c r="R47" t="n">
+        <v>593</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>13093618</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13093618</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>바로선운동센터 판교점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>coolksh11@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 61 2층 201호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/coolksh11</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>183</v>
+      </c>
+      <c r="R48" t="n">
+        <v>205</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2015061102</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2015061102</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>근육연구소</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>musclelab_9609@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1492-9193</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 109 A동 B212호</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/musclelab_9609</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>172</v>
+      </c>
+      <c r="R49" t="n">
+        <v>177</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1655228047</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1655228047</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>이상해GYM PT 판교역점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>isanghaegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1399-9644</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 지2층 B2086호</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@isanghaegym100?si=1UMNdVN5UY8yHcHo</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>124</v>
+      </c>
+      <c r="R50" t="n">
+        <v>190</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1053530808</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1053530808</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>건강한 운동 연구소</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>brave082@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1347-2906</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서판교로44번길 3-14 102호 건강한 운동 연구소</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>6</v>
+      </c>
+      <c r="R51" t="n">
+        <v>20</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1780907875</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1780907875</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>업투 휘트니스 분당판교점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>uptofitness-@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1343-8274</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/uptofitness-</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>618</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>291</v>
+      </c>
+      <c r="R52" t="n">
+        <v>909</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1928497638</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1928497638</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>비아핏</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>viafit@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1379-7507</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교대장로7길 15-2 지하1층,지상1층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viafit_no.1</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>24</v>
+      </c>
+      <c r="R53" t="n">
+        <v>50</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1772663783</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1772663783</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>트친소</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>govlrhaehfdl@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1349-0679</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로2길 9 4층</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/everyworkout/products/5462434513</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>85</v>
+      </c>
+      <c r="R54" t="n">
+        <v>85</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1911382745</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1911382745</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>H GYM PT 대장3호점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>hgym03@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1329-9408</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교대장로 84 304호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://hgym.co.kr</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>111</v>
+      </c>
+      <c r="R55" t="n">
+        <v>222</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1027491629</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1027491629</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>153트레이닝</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>trainerps@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1361-0679</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로3길 36 202호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/everyworkout/products/5462434513</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>19</v>
+      </c>
+      <c r="R56" t="n">
+        <v>20</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1932735845</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1932735845</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>스윗바디</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>superfly3@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>031-701-4327</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로2번길 36 1층 스윗바디</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/superfly3</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>19</v>
+      </c>
+      <c r="R57" t="n">
+        <v>82</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>20364482</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20364482</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>맑음체육관 PT 판교역점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>malgum_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1444-1386</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 3층 305호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/malgum_fitness</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>26</v>
+      </c>
+      <c r="R58" t="n">
+        <v>105</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1424547961</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1424547961</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>휘트니스클럽S 수내점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>fitnessclubs12@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1311-1188</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 백현로101번길 11 5층</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/fitnessclubs12</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>309</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>917</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1226</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1228787055</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1228787055</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>제로퍼스널트레이닝PT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>phh3014@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1341-5808</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 115 판오션타워 501호</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hyunhwa_zero</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>10</v>
+      </c>
+      <c r="R60" t="n">
+        <v>15</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>21647284</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21647284</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>크레이지핏 PT</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>krazyfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1488-5883</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>535</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1437</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1972</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1628554288</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1628554288</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>핏불짐 판교점</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>fitbullgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1430-9683</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2 3층 304호</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/fitbullgym</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>283</v>
+      </c>
+      <c r="R62" t="n">
+        <v>375</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>37814535</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37814535</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>턴핏PT 판교운중점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>sungbin00@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>031-698-4246</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 131 803호, 804호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sungbin00</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>68</v>
+      </c>
+      <c r="R63" t="n">
+        <v>104</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1457398870</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1457398870</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>유앤바디PT 분당수내점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>unbody@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>031-714-4729</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 백현로101번길 12 세인프라자 402호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/unbody</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>166</v>
+      </c>
+      <c r="R64" t="n">
+        <v>284</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1853394852</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1853394852</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>바디수</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>lovelygodus@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>070-8802-9000</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서판교로44번길 15 101호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>http://www.bodysoo.co.kr/</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>11</v>
+      </c>
+      <c r="R65" t="n">
+        <v>16</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>32497004</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32497004</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>구스짐 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>chlgudrn1@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1465-9683</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>143</v>
+      </c>
+      <c r="R66" t="n">
+        <v>306</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1088776551</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1088776551</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>데스런 판교점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>deslun@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1412-6347</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로2번길 38</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>http://www.deslun.co.kr</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>394</v>
+      </c>
+      <c r="R67" t="n">
+        <v>416</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>31469573</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31469573</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>리,무브먼트</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>sujin6735@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1310-5661</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 140 메트로골드 203호</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/re__movement</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>242</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>246</v>
+      </c>
+      <c r="R68" t="n">
+        <v>488</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1149465061</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1149465061</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>판교피트니스센터</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>towershift@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1343-5171</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로289번길 20 3층 판교피트니스센터</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/towershift</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>13</v>
+      </c>
+      <c r="R69" t="n">
+        <v>21</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1874121479</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1874121479</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>좋은습관PTSTUDIO 판교운중</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>goodhabitpg@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1480-0677</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 142 6층</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/goodhabit_pangyo/</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>29</v>
+      </c>
+      <c r="R70" t="n">
+        <v>93</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1070284726</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1070284726</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>열정PT 판교점</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ptpassion@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1319-7157</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로255번길 9-22 우림W-CITY 지하117호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ptpassion</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>208</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>154</v>
+      </c>
+      <c r="R71" t="n">
+        <v>362</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1614896755</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1614896755</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>원프로짐PT</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>onepro_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1304-9363</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서판교로 164 훼미리프라자 402호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oneprogym_seopangyo</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>35</v>
+      </c>
+      <c r="R72" t="n">
+        <v>49</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1663447864</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1663447864</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>뱅핏 PT 판교운중점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>bangfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1345-4609</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 122 골드클래스 8층 801호, 802호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bangfit_official</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>245</v>
+      </c>
+      <c r="R73" t="n">
+        <v>310</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1890400282</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1890400282</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>리조트휘트니스 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>resort_5@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1438-0677</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/resortfitness__pangyo/</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>413</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>714</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1127</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>35524502</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35524502</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>팀제이맥스 피티 서현점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>teamjmax_sh@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>031-702-8296</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로180번길 13 2층 206호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/teamjmax_sh</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>911</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>549</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1460</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1639683746</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1639683746</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>솔리드짐 PT 수내점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ppapers@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1420-7858</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로258번길 10-7 403호</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/solid_gym1</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>652</v>
+      </c>
+      <c r="R76" t="n">
+        <v>797</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1205679892</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1205679892</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/판교_헬스장.xlsx
+++ b/naver-place-crawler/results_health/판교_헬스장.xlsx
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>그라운드피트니스</t>
+          <t>밥스짐 분당점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ground-fitness@naver.com</t>
+          <t>ish0674@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1464-5758</t>
+          <t>0507-1474-7017</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 170 풍림아이원플러스 3층 301호</t>
+          <t>경기도 성남시 분당구 성남대로 449 로얄팰리스 에이동 212, 213, 214호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ground-fitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="Q2" t="n">
-        <v>1211</v>
+        <v>185</v>
       </c>
       <c r="R2" t="n">
-        <v>1585</v>
+        <v>267</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1472483345</t>
+          <t>1581057750</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1472483345</t>
+          <t>https://m.place.naver.com/place/1581057750</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>레조나헬스랩PT 서판교점</t>
+          <t>PDC스포츠센터</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>resonar_healthlab@naver.com</t>
+          <t>spxkzjs12@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1411-1104</t>
+          <t>031-8060-0377</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
+          <t>경기도 성남시 분당구 판교로 242 판교디지털센터 A동 2층 PDC스포츠센터</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resonar_healthlab</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="Q3" t="n">
-        <v>202</v>
+        <v>19</v>
       </c>
       <c r="R3" t="n">
-        <v>258</v>
+        <v>71</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1644348689</t>
+          <t>1057141943</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1644348689</t>
+          <t>https://m.place.naver.com/place/1057141943</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +747,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>하이퀄짐 헬스PT 판교점</t>
+          <t>짐라이언피트니스 수내역1호점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>highqualgym@naver.com</t>
+          <t>liongym1@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1364-9601</t>
+          <t>0507-1319-1102</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 128 2층</t>
+          <t>경기도 성남시 분당구 수내로46번길 11 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/highqualgym2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -794,10 +794,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fux6</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>58</v>
+        <v>1701</v>
       </c>
       <c r="Q4" t="n">
-        <v>103</v>
+        <v>343</v>
       </c>
       <c r="R4" t="n">
-        <v>161</v>
+        <v>2044</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1012638231</t>
+          <t>1628575924</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1012638231</t>
+          <t>https://m.place.naver.com/place/1628575924</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,34 +850,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>밥스짐 분당점</t>
+          <t>버핏그라운드 판교벤처타운</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ish0674@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1474-7017</t>
+          <t>0507-1315-3624</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로 449 로얄팰리스 에이동 212, 213, 214호</t>
+          <t>경기도 성남시 분당구 대왕판교로644번길 49 B2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bobsgymbob/profilecard/?igsh=MTFxcDRvanRsZ2ZyNA==</t>
+          <t>https://www.butfitground.com/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,18 +891,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzq100p</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="Q5" t="n">
-        <v>185</v>
+        <v>29</v>
       </c>
       <c r="R5" t="n">
-        <v>267</v>
+        <v>140</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1581057750</t>
+          <t>2064425838</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1581057750</t>
+          <t>https://m.place.naver.com/place/2064425838</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,20 +952,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>봇들마을8단지한신휴플러스아파트휘트니스센터</t>
+          <t>피트니스패밀리</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1logdesign@naver.com</t>
+          <t>tkdkrkwl@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>031-739-7188</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 153</t>
+          <t>경기도 성남시 분당구 대왕판교로712번길 22</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -993,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1443133117</t>
+          <t>30817753</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1443133117</t>
+          <t>https://m.place.naver.com/place/30817753</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1025,34 +1041,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>런던피트니스&amp;필라테스 분당이매점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>londoner83@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1406-9679</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1062,20 +1078,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pnpp</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1087,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2540</v>
+        <v>1340</v>
       </c>
       <c r="Q7" t="n">
-        <v>323</v>
+        <v>473</v>
       </c>
       <c r="R7" t="n">
-        <v>2863</v>
+        <v>1813</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>13530251</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/13530251</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1119,34 +1139,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>엔엘휘트니스 분당이매점</t>
+          <t>헬스보이짐&amp;필라걸 수내점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nlfitness2@naver.com</t>
+          <t>healthboy40@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1415-2075</t>
+          <t>0507-1380-2239</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 440 지하1층</t>
+          <t>경기도 성남시 분당구 내정로173번길 49 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nlfitness2_imae/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1156,7 +1176,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1166,10 +1186,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4laa0</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1181,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>642</v>
+        <v>968</v>
       </c>
       <c r="Q8" t="n">
-        <v>241</v>
+        <v>734</v>
       </c>
       <c r="R8" t="n">
-        <v>883</v>
+        <v>1702</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1194690742</t>
+          <t>1973151166</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1194690742</t>
+          <t>https://m.place.naver.com/place/1973151166</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1213,34 +1237,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;필라걸 수내점</t>
+          <t>고릴라멀티짐 분당서현점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>healthboy40@naver.com</t>
+          <t>gorillagym6@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1380-2239</t>
+          <t>0507-1373-0880</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 내정로173번길 49 5층</t>
+          <t>경기도 성남시 분당구 서현로 192 야베스벨리 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy40/223688037867</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1250,20 +1274,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4p3i52</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1275,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>968</v>
+        <v>652</v>
       </c>
       <c r="Q9" t="n">
-        <v>734</v>
+        <v>949</v>
       </c>
       <c r="R9" t="n">
-        <v>1702</v>
+        <v>1601</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1973151166</t>
+          <t>31457116</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973151166</t>
+          <t>https://m.place.naver.com/place/31457116</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1312,34 +1340,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>헤일로짐24시 헬스 PT 판교점</t>
+          <t>산운휘트니스센타</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>halogym02@naver.com</t>
+          <t>hak0234@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1315-8840</t>
+          <t>0507-1405-9688</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+          <t>경기도 성남시 분당구 판교원로 68</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/933331</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1349,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1360,7 +1388,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1369,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>663</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>929</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1592</v>
+        <v>3</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1806695299</t>
+          <t>20123481</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806695299</t>
+          <t>https://m.place.naver.com/place/20123481</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1406,39 +1434,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>커스텀핏 PT</t>
+          <t>휘트니스클럽S 이매점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>customfitpt@naver.com</t>
+          <t>fitnessclubs10@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>031-8016-5677</t>
+          <t>0507-1442-7786</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 123 마크시티 오렌지동 3층</t>
+          <t>경기도 성남시 분당구 판교로 446 그린프라자 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/https://booking.naver.com/booking/5/bizes/795160/items/4714422?preview=1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1448,10 +1476,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4n4uy</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1459,17 +1491,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>199</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>525</v>
       </c>
       <c r="R11" t="n">
-        <v>5</v>
+        <v>724</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,12 +1510,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>35644006</t>
+          <t>38673070</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35644006</t>
+          <t>https://m.place.naver.com/place/38673070</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1495,34 +1527,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>바디센서리 판교점 헬스PT</t>
+          <t>업투휘트니스 분당삼평점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bodysensory@naver.com</t>
+          <t>upto_sampyeong@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1344-2096</t>
+          <t>0507-1466-1103</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 41 프라임스퀘어 10층</t>
+          <t>경기도 성남시 분당구 판교로 375 4층 401-2,402~405호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/BumGi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1532,7 +1564,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1542,10 +1574,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fc6k</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1557,13 +1593,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>46</v>
+        <v>562</v>
       </c>
       <c r="Q12" t="n">
-        <v>292</v>
+        <v>555</v>
       </c>
       <c r="R12" t="n">
-        <v>338</v>
+        <v>1117</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,12 +1608,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1786901360</t>
+          <t>1878300058</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1786901360</t>
+          <t>https://m.place.naver.com/place/1878300058</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1589,64 +1625,64 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교벤처타운</t>
+          <t>레조나헬스랩PT 서판교점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>resonar_healthlab@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1315-3624</t>
+          <t>0507-1411-1104</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로644번길 49 B2층</t>
+          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42t22</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1655,13 +1691,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>111</v>
+        <v>56</v>
       </c>
       <c r="Q13" t="n">
-        <v>29</v>
+        <v>202</v>
       </c>
       <c r="R13" t="n">
-        <v>140</v>
+        <v>258</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,12 +1706,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2064425838</t>
+          <t>1644348689</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064425838</t>
+          <t>https://m.place.naver.com/place/1644348689</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1692,29 +1728,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>런던피트니스&amp;필라테스 분당이매점</t>
+          <t>F45 서현</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>londoner83@naver.com</t>
+          <t>ssun_mom@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1406-9679</t>
+          <t>031-702-4520</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
+          <t>경기도 성남시 분당구 황새울로342번길 21 대정빌딩 지하 1층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/londoner83</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1724,20 +1760,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w467wn</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>X</t>
@@ -1749,13 +1789,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1340</v>
+        <v>468</v>
       </c>
       <c r="Q14" t="n">
-        <v>473</v>
+        <v>96</v>
       </c>
       <c r="R14" t="n">
-        <v>1813</v>
+        <v>564</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,12 +1804,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>13530251</t>
+          <t>1316630678</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13530251</t>
+          <t>https://m.place.naver.com/place/1316630678</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1781,34 +1821,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>익스홀릭 가넷 이매점</t>
+          <t>하이퀄짐 헬스PT 판교점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>exholicimae@naver.com</t>
+          <t>highqualgym@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1450-3374</t>
+          <t>0507-1364-9601</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 이매로 45 이수프라자</t>
+          <t>경기도 성남시 분당구 운중로 128 2층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/exholicimae</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1818,20 +1858,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w406tf</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>X</t>
@@ -1843,13 +1887,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>310</v>
+        <v>58</v>
       </c>
       <c r="Q15" t="n">
-        <v>228</v>
+        <v>103</v>
       </c>
       <c r="R15" t="n">
-        <v>538</v>
+        <v>161</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,12 +1902,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>21281338</t>
+          <t>1012638231</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21281338</t>
+          <t>https://m.place.naver.com/place/1012638231</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1880,29 +1924,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>스포애니 서현역점</t>
+          <t>봇들마을8단지한신휴플러스아파트휘트니스센터</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>spoany22@naver.com</t>
+          <t>1logdesign@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>031-706-8522</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로 324 좋은상호저축은행빌딩 B1층</t>
+          <t>경기도 성남시 분당구 동판교로 153</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany22</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1912,12 +1952,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1933,17 +1973,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2036</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>2986</v>
+        <v>1</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,12 +1992,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>13025013</t>
+          <t>1443133117</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13025013</t>
+          <t>https://m.place.naver.com/place/1443133117</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1974,25 +2014,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>팀버핏 판교</t>
+          <t>헤일로짐24시 헬스 PT 판교점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
+          <t>halogym02@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1315-8840</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하3층 B3008</t>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/butfitground</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2002,38 +2046,42 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfevb4</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>236</v>
+        <v>663</v>
       </c>
       <c r="Q17" t="n">
-        <v>95</v>
+        <v>929</v>
       </c>
       <c r="R17" t="n">
-        <v>331</v>
+        <v>1592</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,12 +2090,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1004612269</t>
+          <t>1806695299</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1004612269</t>
+          <t>https://m.place.naver.com/place/1806695299</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2106,10 +2154,14 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41p6u</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>X</t>
@@ -2158,29 +2210,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>F45 판교</t>
+          <t>익스홀릭 가넷 이매점</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ksh1992001@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>pangyo.admin@f45training.kr</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>exholicimae@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1450-3374</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하 1층 119-6호</t>
+          <t>경기도 성남시 분당구 이매로 45 이수프라자</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>http://www.f45training.kr/pangyo</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2200,10 +2252,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47rcx</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>X</t>
@@ -2215,13 +2271,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>103</v>
+        <v>310</v>
       </c>
       <c r="Q19" t="n">
-        <v>105</v>
+        <v>228</v>
       </c>
       <c r="R19" t="n">
-        <v>208</v>
+        <v>538</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,12 +2286,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1017940051</t>
+          <t>21281338</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1017940051</t>
+          <t>https://m.place.naver.com/place/21281338</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2252,29 +2308,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>스포짐 판교역점</t>
+          <t>클럽 브릭스 판교</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>showmethecash@naver.com</t>
+          <t>lulusoul22@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1436-1236</t>
+          <t>031-625-5566</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 117 B101호</t>
+          <t>경기도 성남시 분당구 분당내곡로 131 판교테크원타워 B1 클럽브릭스</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spogym_p.g/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2284,7 +2340,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2294,10 +2350,14 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wolfmmb</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>X</t>
@@ -2309,13 +2369,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1252</v>
+        <v>331</v>
       </c>
       <c r="Q20" t="n">
-        <v>641</v>
+        <v>94</v>
       </c>
       <c r="R20" t="n">
-        <v>1893</v>
+        <v>425</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,12 +2384,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1088507385</t>
+          <t>1141858723</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088507385</t>
+          <t>https://m.place.naver.com/place/1141858723</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2346,29 +2406,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PDC스포츠센터</t>
+          <t>F45 판교</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>spxkzjs12@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>031-8060-0377</t>
-        </is>
-      </c>
+          <t>ksh1992001@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>pangyo.admin@f45training.kr</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 242 판교디지털센터 A동 2층 PDC스포츠센터</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하 1층 119-6호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.f45training.kr/pangyo</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2399,17 +2459,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="Q21" t="n">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="R21" t="n">
-        <v>71</v>
+        <v>208</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,12 +2478,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1057141943</t>
+          <t>1017940051</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1057141943</t>
+          <t>https://m.place.naver.com/place/1017940051</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2440,29 +2500,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>짐라이언피트니스 수내역1호점</t>
+          <t>스타디온 판교 크로스핏</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>liongym1@naver.com</t>
+          <t>sbkim10@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1319-1102</t>
+          <t>031-603-1109</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 수내로46번길 11 지하1층</t>
+          <t>경기도 성남시 분당구 동판교로177번길 25 지하B103호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymlion_sunae</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2472,7 +2532,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2497,13 +2557,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1701</v>
+        <v>114</v>
       </c>
       <c r="Q22" t="n">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="R22" t="n">
-        <v>2044</v>
+        <v>440</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2512,12 +2572,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1628575924</t>
+          <t>1332230479</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628575924</t>
+          <t>https://m.place.naver.com/place/1332230479</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2534,29 +2594,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>클럽 브릭스 판교</t>
+          <t>스포애니 서현역점</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>club_breex@naver.com</t>
+          <t>spoany22@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>031-625-5566</t>
+          <t>031-706-8522</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 131 판교테크원타워 B1 클럽브릭스</t>
+          <t>경기도 성남시 분당구 황새울로 324 좋은상호저축은행빌딩 B1층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/club_breex</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2566,20 +2626,24 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40q6m</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>X</t>
@@ -2591,13 +2655,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>331</v>
+        <v>951</v>
       </c>
       <c r="Q23" t="n">
-        <v>94</v>
+        <v>2036</v>
       </c>
       <c r="R23" t="n">
-        <v>425</v>
+        <v>2987</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2606,12 +2670,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1141858723</t>
+          <t>13025013</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1141858723</t>
+          <t>https://m.place.naver.com/place/13025013</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2628,24 +2692,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>산운휘트니스센타</t>
+          <t>스포짐 판교점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>gusdk021@naver.com</t>
+          <t>spogym7@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1405-9688</t>
+          <t>0507-1476-8384</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교원로 68</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2670,10 +2734,14 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wpasubw</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>X</t>
@@ -2681,17 +2749,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>623</v>
       </c>
       <c r="R24" t="n">
-        <v>3</v>
+        <v>1354</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2700,12 +2768,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>20123481</t>
+          <t>20123697</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20123481</t>
+          <t>https://m.place.naver.com/place/20123697</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2722,24 +2790,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>피트니스패밀리</t>
+          <t>엔엘휘트니스 분당이매점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>tkdkrkwl@naver.com</t>
+          <t>makefit4@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>031-739-7188</t>
+          <t>0507-1415-2075</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로712번길 22</t>
+          <t>경기도 성남시 분당구 판교로 440 지하1층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2764,10 +2832,14 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdo0ttk</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>X</t>
@@ -2775,17 +2847,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>643</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>241</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>884</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2794,12 +2866,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>30817753</t>
+          <t>1194690742</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/30817753</t>
+          <t>https://m.place.naver.com/place/1194690742</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2816,29 +2888,33 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>헬스플러스 판교5호점</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>healthplus_pangyo5@naver.com</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1313-1507</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 2 지하1층</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthplus_pangyo5/</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2853,18 +2929,22 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42raj</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2873,13 +2953,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>674</v>
+        <v>1765</v>
       </c>
       <c r="Q26" t="n">
-        <v>1070</v>
+        <v>250</v>
       </c>
       <c r="R26" t="n">
-        <v>1744</v>
+        <v>2015</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2888,12 +2968,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1086359388</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1086359388</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2910,34 +2990,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>휘트니스클럽S 이매점</t>
+          <t>파크뷰휘트니스클럽</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>fitnessclubs10@naver.com</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>parkviewf1004@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>parkview.f.1004@gmail.com</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1442-7786</t>
+          <t>031-783-3000</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 446 그린프라자 3층</t>
+          <t>경기도 성남시 분당구 정자일로 248 파크뷰상가 3층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitnessclubs10</t>
+          <t>https://www.parkviewfc.co.kr</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2958,7 +3042,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2967,13 +3051,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>199</v>
+        <v>48</v>
       </c>
       <c r="Q27" t="n">
-        <v>525</v>
+        <v>127</v>
       </c>
       <c r="R27" t="n">
-        <v>724</v>
+        <v>175</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2982,12 +3066,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>38673070</t>
+          <t>11847077</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38673070</t>
+          <t>https://m.place.naver.com/place/11847077</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3004,29 +3088,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>고릴라멀티짐 분당서현점</t>
+          <t>헬스플러스 판교5호점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>gorillagym6@naver.com</t>
+          <t>healthplus_pangyo5@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1373-0880</t>
+          <t>0507-1313-1507</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로 192 야베스벨리 5층</t>
+          <t>경기도 성남시 분당구 판교공원로2길 2 지하1층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gorillamultigym_bundangseohyun?igsh=cWMyMDFqYjZsdjg5&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3036,7 +3120,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3046,10 +3130,14 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t89k</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>X</t>
@@ -3061,13 +3149,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>652</v>
+        <v>674</v>
       </c>
       <c r="Q28" t="n">
-        <v>949</v>
+        <v>1071</v>
       </c>
       <c r="R28" t="n">
-        <v>1601</v>
+        <v>1745</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3076,12 +3164,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>31457116</t>
+          <t>1086359388</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31457116</t>
+          <t>https://m.place.naver.com/place/1086359388</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3098,38 +3186,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>운동공간픽스앤빌드</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>physio_congmi@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1433-4667</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 산운로160번길 10 1층 101호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://www.themosttimes.co.kr/39064</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3139,18 +3223,22 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wb5l72t</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3159,13 +3247,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1765</v>
+        <v>64</v>
       </c>
       <c r="Q29" t="n">
-        <v>250</v>
+        <v>430</v>
       </c>
       <c r="R29" t="n">
-        <v>2015</v>
+        <v>494</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3174,12 +3262,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1637759423</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1637759423</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3196,29 +3284,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>F45 서현</t>
+          <t>원팀짐</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>yerim1118@naver.com</t>
+          <t>makefitness3@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>031-702-4520</t>
+          <t>031-702-2070</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로342번길 21 대정빌딩 지하 1층</t>
+          <t>경기도 성남시 분당구 운중로 128 7층 701호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45_seohyeon/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3228,7 +3316,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3238,10 +3326,14 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wl0ubx8</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>X</t>
@@ -3253,13 +3345,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="Q30" t="n">
-        <v>96</v>
+        <v>289</v>
       </c>
       <c r="R30" t="n">
-        <v>564</v>
+        <v>781</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3268,12 +3360,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1316630678</t>
+          <t>1973455447</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1316630678</t>
+          <t>https://m.place.naver.com/place/1973455447</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3290,29 +3382,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>원팀짐</t>
+          <t>스포짐 판교역점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>oneteamgym-@naver.com</t>
+          <t>showmethecash@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>031-702-2070</t>
+          <t>0507-1436-1236</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 128 7층 701호</t>
+          <t>경기도 성남시 분당구 분당내곡로 117 B101호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oneteamgym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3322,7 +3414,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3332,10 +3424,14 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w444pd</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>X</t>
@@ -3347,13 +3443,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>492</v>
+        <v>1253</v>
       </c>
       <c r="Q31" t="n">
-        <v>289</v>
+        <v>641</v>
       </c>
       <c r="R31" t="n">
-        <v>781</v>
+        <v>1894</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3362,12 +3458,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1973455447</t>
+          <t>1088507385</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973455447</t>
+          <t>https://m.place.naver.com/place/1088507385</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3384,29 +3480,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>크로스핏 라운지</t>
+          <t>팀버핏 판교</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>crossfit_lounge@naver.com</t>
+          <t>teambutfit@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0507-1321-6851</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로319번길 8-4 지하1층</t>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하3층 B3008</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/crossfit_lounge</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3416,12 +3508,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3441,13 +3533,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="Q32" t="n">
-        <v>271</v>
+        <v>95</v>
       </c>
       <c r="R32" t="n">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3456,12 +3548,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2067270233</t>
+          <t>1004612269</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2067270233</t>
+          <t>https://m.place.naver.com/place/1004612269</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3473,64 +3565,64 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>파크뷰휘트니스클럽</t>
+          <t>바디센서리 판교점 헬스PT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>parkviewf1004@naver.com</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>parkview.f.1004@gmail.com</t>
-        </is>
-      </c>
+          <t>bodysensory@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>031-783-3000</t>
+          <t>0507-1344-2096</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 248 파크뷰상가 3층</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 41 프라임스퀘어 10층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.parkviewfc.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4124s</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3539,13 +3631,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q33" t="n">
-        <v>127</v>
+        <v>292</v>
       </c>
       <c r="R33" t="n">
-        <v>175</v>
+        <v>338</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3554,12 +3646,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>11847077</t>
+          <t>1786901360</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11847077</t>
+          <t>https://m.place.naver.com/place/1786901360</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3576,39 +3668,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>운동공간픽스앤빌드</t>
+          <t>커스텀핏 PT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>physio_congmi@naver.com</t>
+          <t>customfitpt@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1433-4667</t>
+          <t>031-8016-5677</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 산운로160번길 10 1층 101호</t>
+          <t>경기도 성남시 분당구 운중로 123 마크시티 오렌지동 3층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.themosttimes.co.kr/39064</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3629,17 +3721,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>430</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>494</v>
+        <v>5</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3648,12 +3740,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1637759423</t>
+          <t>35644006</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1637759423</t>
+          <t>https://m.place.naver.com/place/35644006</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3670,29 +3762,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>스포짐 판교점</t>
+          <t>그라운드피트니스</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>spogym_2@naver.com</t>
+          <t>ground-fitness@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1476-8384</t>
+          <t>0507-1464-5758</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
+          <t>경기도 성남시 분당구 서현로 170 풍림아이원플러스 3층 301호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spogym_pg</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3702,7 +3794,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3712,13 +3804,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a0s5</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3727,13 +3823,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>731</v>
+        <v>374</v>
       </c>
       <c r="Q35" t="n">
-        <v>624</v>
+        <v>1211</v>
       </c>
       <c r="R35" t="n">
-        <v>1355</v>
+        <v>1585</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3742,12 +3838,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>20123697</t>
+          <t>1472483345</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20123697</t>
+          <t>https://m.place.naver.com/place/1472483345</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3764,29 +3860,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>업투휘트니스 분당삼평점</t>
+          <t>크로스핏 라운지</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>upto_sampyeong@naver.com</t>
+          <t>crossfit_lounge@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1466-1103</t>
+          <t>0507-1321-6851</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 375 4층 401-2,402~405호</t>
+          <t>경기도 성남시 분당구 황새울로319번길 8-4 지하1층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/upto_sampyeong</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3796,20 +3892,24 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wad8v4j</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
           <t>X</t>
@@ -3821,13 +3921,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>562</v>
+        <v>43</v>
       </c>
       <c r="Q36" t="n">
-        <v>555</v>
+        <v>271</v>
       </c>
       <c r="R36" t="n">
-        <v>1117</v>
+        <v>314</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3836,12 +3936,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1878300058</t>
+          <t>2067270233</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1878300058</t>
+          <t>https://m.place.naver.com/place/2067270233</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -3853,34 +3953,34 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>트랜스핏짐 서현역점</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>transfit_gym@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1387-9682</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당로53번길 15 지하1층 트랜스핏짐 서현역점</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/transfit_gym</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3915,13 +4015,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2191</v>
+        <v>2540</v>
       </c>
       <c r="Q37" t="n">
-        <v>2247</v>
+        <v>323</v>
       </c>
       <c r="R37" t="n">
-        <v>4438</v>
+        <v>2863</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3930,12 +4030,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1487183442</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487183442</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3952,29 +4052,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>스타디온 판교 크로스핏</t>
+          <t>트랜스핏짐 서현역점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>sbkim10@naver.com</t>
+          <t>transfit_gym@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>031-603-1109</t>
+          <t>0507-1387-9682</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로177번길 25 지하B103호</t>
+          <t>경기도 성남시 분당구 분당로53번길 15 지하1층 트랜스핏짐 서현역점</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/stadion_pangyo_crossfit?igsh=MXg2azI4ZjFsemtkMw%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3984,7 +4084,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3994,10 +4094,14 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4r1p3</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
           <t>X</t>
@@ -4009,13 +4113,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>114</v>
+        <v>2191</v>
       </c>
       <c r="Q38" t="n">
-        <v>326</v>
+        <v>2246</v>
       </c>
       <c r="R38" t="n">
-        <v>440</v>
+        <v>4437</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4024,12 +4128,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1332230479</t>
+          <t>1487183442</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1332230479</t>
+          <t>https://m.place.naver.com/place/1487183442</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4046,33 +4150,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 판교</t>
+          <t>크레이지핏 PT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>krazyfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1417-1133</t>
+          <t>0507-1488-5883</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4082,7 +4182,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4107,13 +4207,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>535</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1437</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1972</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4122,12 +4222,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2029680813</t>
+          <t>1628554288</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029680813</t>
+          <t>https://m.place.naver.com/place/1628554288</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4144,29 +4244,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>H GYM PT GT 판교2호점</t>
+          <t>바디수</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>hgym9408@naver.com</t>
+          <t>lovelygodus@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1353-9408</t>
+          <t>070-8802-9000</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 233 302호</t>
+          <t>경기도 성남시 분당구 서판교로44번길 15 101호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://hgym.imweb.me</t>
+          <t>http://www.bodysoo.co.kr/</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4176,12 +4276,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4201,13 +4301,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>279</v>
+        <v>5</v>
       </c>
       <c r="Q40" t="n">
-        <v>419</v>
+        <v>11</v>
       </c>
       <c r="R40" t="n">
-        <v>698</v>
+        <v>16</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4216,12 +4316,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1850894755</t>
+          <t>32497004</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850894755</t>
+          <t>https://m.place.naver.com/place/32497004</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4238,29 +4338,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>피티스튜디오이룸 PT EROOM</t>
+          <t>리,무브먼트</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ptstudioeroom@naver.com</t>
+          <t>sujin6735@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1361-7934</t>
+          <t>0507-1310-5661</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 45 3층 303호</t>
+          <t>경기도 성남시 분당구 운중로 140 메트로골드 203호</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ptstudioeroom</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4270,23 +4370,27 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ag69</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4295,13 +4399,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>46</v>
+        <v>242</v>
       </c>
       <c r="Q41" t="n">
-        <v>32</v>
+        <v>246</v>
       </c>
       <c r="R41" t="n">
-        <v>78</v>
+        <v>488</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4310,12 +4414,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1164280530</t>
+          <t>1149465061</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1164280530</t>
+          <t>https://m.place.naver.com/place/1149465061</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4332,29 +4436,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>핏앤클래시 PT</t>
+          <t>린바디핏 PT 판교본점</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>fitclassy22@naver.com</t>
+          <t>leanbodyfitv2@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1325-5251</t>
+          <t>0507-1302-8312</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로 154 낙생빌딩 201호</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 지하113호</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitclassy22</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4364,38 +4468,42 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3fqoyd</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="Q42" t="n">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="R42" t="n">
-        <v>65</v>
+        <v>243</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4404,12 +4512,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1283224823</t>
+          <t>1699238533</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1283224823</t>
+          <t>https://m.place.naver.com/place/1699238533</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4426,29 +4534,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>에너지플로우짐</t>
+          <t>H GYM PT 대장3호점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>exerscience@naver.com</t>
+          <t>hgym9408@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1346-9129</t>
+          <t>0507-1329-9408</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 230 B동 지하1층 B126-1호</t>
+          <t>경기도 성남시 분당구 판교대장로 84 304호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://energyflowlab.my.canva.site</t>
+          <t>https://hgym.co.kr</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4458,20 +4566,24 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4aih7</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
           <t>X</t>
@@ -4483,13 +4595,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="Q43" t="n">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="R43" t="n">
-        <v>39</v>
+        <v>222</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4498,12 +4610,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1846760075</t>
+          <t>1027491629</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1846760075</t>
+          <t>https://m.place.naver.com/place/1027491629</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4520,35 +4632,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>여성전용 비조 필라PT 자이로토닉</t>
+          <t>유앤바디PT 분당수내점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>viyulgallery@naver.com</t>
+          <t>unbody@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>031-714-4729</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 132</t>
+          <t>경기도 성남시 분당구 백현로101번길 12 세인프라자 402호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.themosttimes.co.kr/43811</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4558,10 +4674,14 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4b6la</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>X</t>
@@ -4569,17 +4689,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="Q44" t="n">
-        <v>50</v>
+        <v>166</v>
       </c>
       <c r="R44" t="n">
-        <v>179</v>
+        <v>284</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4588,12 +4708,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1600591794</t>
+          <t>1853394852</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1600591794</t>
+          <t>https://m.place.naver.com/place/1853394852</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4610,20 +4730,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>엑서사이언스짐</t>
+          <t>판교피트니스센터</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>exerscience@naver.com</t>
+          <t>towershift@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1343-5171</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 240 삼환하이펙스A동 B1층 B117-1호</t>
+          <t>경기도 성남시 분당구 판교로289번길 20 3층 판교피트니스센터</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4659,17 +4783,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q45" t="n">
-        <v>143</v>
+        <v>13</v>
       </c>
       <c r="R45" t="n">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4678,12 +4802,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1746641680</t>
+          <t>1874121479</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1746641680</t>
+          <t>https://m.place.naver.com/place/1874121479</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -4700,39 +4824,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>린바디핏 PT 판교본점</t>
+          <t>H GYM PT GT 판교2호점</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>leanbodyfitv2@naver.com</t>
+          <t>hgym9408@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1302-8312</t>
+          <t>0507-1353-9408</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 지하113호</t>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/leanbodyfitv2</t>
+          <t>https://hgym.imweb.me</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4742,28 +4866,32 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47alh</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>135</v>
+        <v>279</v>
       </c>
       <c r="Q46" t="n">
-        <v>108</v>
+        <v>419</v>
       </c>
       <c r="R46" t="n">
-        <v>243</v>
+        <v>698</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4772,12 +4900,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1699238533</t>
+          <t>1850894755</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699238533</t>
+          <t>https://m.place.naver.com/place/1850894755</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4794,39 +4922,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>피티세븐 퍼스널트레이닝</t>
+          <t>핏앤클래시 PT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>body2balance@naver.com</t>
+          <t>fitclassy22@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1400-9428</t>
+          <t>0507-1325-5251</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로132번길 22-1 1층 102호 피티세븐</t>
+          <t>경기도 성남시 분당구 서판교로 154 낙생빌딩 201호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>http://www.pts7.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4836,13 +4964,17 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45ryz</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4851,13 +4983,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>302</v>
+        <v>43</v>
       </c>
       <c r="Q47" t="n">
-        <v>291</v>
+        <v>22</v>
       </c>
       <c r="R47" t="n">
-        <v>593</v>
+        <v>65</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4866,12 +4998,12 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>13093618</t>
+          <t>1283224823</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13093618</t>
+          <t>https://m.place.naver.com/place/1283224823</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -4944,10 +5076,10 @@
         <v>22</v>
       </c>
       <c r="Q48" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="R48" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4978,29 +5110,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>근육연구소</t>
+          <t>스윗바디</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>musclelab_9609@naver.com</t>
+          <t>superfly3@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1492-9193</t>
+          <t>031-701-4327</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 109 A동 B212호</t>
+          <t>경기도 성남시 분당구 판교역로2번길 36 1층 스윗바디</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/musclelab_9609</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5010,20 +5142,24 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5whn9</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
           <t>X</t>
@@ -5035,13 +5171,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="Q49" t="n">
-        <v>172</v>
+        <v>19</v>
       </c>
       <c r="R49" t="n">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5050,12 +5186,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1655228047</t>
+          <t>20364482</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1655228047</t>
+          <t>https://m.place.naver.com/place/20364482</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5094,17 +5230,17 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://youtube.com/@isanghaegym100?si=1UMNdVN5UY8yHcHo</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5114,10 +5250,14 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w1cs1tt</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
           <t>X</t>
@@ -5166,24 +5306,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>건강한 운동 연구소</t>
+          <t>제로퍼스널트레이닝PT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>brave082@naver.com</t>
+          <t>phh3014@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1347-2906</t>
+          <t>0507-1341-5808</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로44번길 3-14 102호 건강한 운동 연구소</t>
+          <t>경기도 성남시 분당구 운중로 115 판오션타워 501호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5208,10 +5348,14 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41tad</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>X</t>
@@ -5219,17 +5363,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R51" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5238,12 +5382,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1780907875</t>
+          <t>21647284</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1780907875</t>
+          <t>https://m.place.naver.com/place/21647284</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5260,29 +5404,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>업투 휘트니스 분당판교점</t>
+          <t>구스짐 PT 판교점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>uptofitness-@naver.com</t>
+          <t>chlgudrn1@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1343-8274</t>
+          <t>0507-1465-9683</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/uptofitness-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5292,20 +5436,24 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyuehl2</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>X</t>
@@ -5317,13 +5465,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>618</v>
+        <v>163</v>
       </c>
       <c r="Q52" t="n">
-        <v>291</v>
+        <v>143</v>
       </c>
       <c r="R52" t="n">
-        <v>909</v>
+        <v>306</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5332,12 +5480,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1928497638</t>
+          <t>1088776551</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928497638</t>
+          <t>https://m.place.naver.com/place/1088776551</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5354,29 +5502,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>비아핏</t>
+          <t>휘트니스클럽S 수내점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>viafit@naver.com</t>
+          <t>fitnessclubs12@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1379-7507</t>
+          <t>0507-1311-1188</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로7길 15-2 지하1층,지상1층</t>
+          <t>경기도 성남시 분당구 백현로101번길 11 5층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/viafit_no.1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5386,7 +5534,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5396,10 +5544,14 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49zvx</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>X</t>
@@ -5411,13 +5563,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>26</v>
+        <v>309</v>
       </c>
       <c r="Q53" t="n">
-        <v>24</v>
+        <v>917</v>
       </c>
       <c r="R53" t="n">
-        <v>50</v>
+        <v>1226</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5426,12 +5578,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1772663783</t>
+          <t>1228787055</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1772663783</t>
+          <t>https://m.place.naver.com/place/1228787055</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5448,29 +5600,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>트친소</t>
+          <t>원프로짐PT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>govlrhaehfdl@naver.com</t>
+          <t>onepro_gym@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1349-0679</t>
+          <t>0507-1304-9363</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로2길 9 4층</t>
+          <t>경기도 성남시 분당구 서판교로 164 훼미리프라자 402호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/everyworkout/products/5462434513</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5480,7 +5632,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5490,10 +5642,14 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wd5irjz</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>X</t>
@@ -5501,17 +5657,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q54" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="R54" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5520,12 +5676,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1911382745</t>
+          <t>1663447864</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1911382745</t>
+          <t>https://m.place.naver.com/place/1663447864</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5542,29 +5698,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>H GYM PT 대장3호점</t>
+          <t>여성전용 비조 필라PT 자이로토닉</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>hgym03@naver.com</t>
+          <t>viyulgallery@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0507-1329-9408</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교대장로 84 304호</t>
+          <t>경기도 성남시 분당구 운중로 132</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://hgym.co.kr</t>
+          <t>https://www.themosttimes.co.kr/43811</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5574,20 +5726,24 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4642d</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
           <t>X</t>
@@ -5595,17 +5751,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="Q55" t="n">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="R55" t="n">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5614,12 +5770,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1027491629</t>
+          <t>1600591794</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1027491629</t>
+          <t>https://m.place.naver.com/place/1600591794</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -5636,29 +5792,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>153트레이닝</t>
+          <t>열정PT 판교점</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>trainerps@naver.com</t>
+          <t>ptpassion@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1361-0679</t>
+          <t>0507-1319-7157</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교공원로3길 36 202호</t>
+          <t>경기도 성남시 분당구 판교로255번길 9-22 우림W-CITY 지하117호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/everyworkout/products/5462434513</t>
+          <t>https://blog.naver.com/ptpassion</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5673,7 +5829,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5689,17 +5845,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1</v>
+        <v>208</v>
       </c>
       <c r="Q56" t="n">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="R56" t="n">
-        <v>20</v>
+        <v>362</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5708,12 +5864,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1932735845</t>
+          <t>1614896755</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1932735845</t>
+          <t>https://m.place.naver.com/place/1614896755</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5730,29 +5886,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>스윗바디</t>
+          <t>피티스튜디오이룸 PT EROOM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>superfly3@naver.com</t>
+          <t>ptstudioeroom@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>031-701-4327</t>
+          <t>0507-1361-7934</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로2번길 36 1층 스윗바디</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 45 3층 303호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/superfly3</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5762,23 +5918,27 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wuyghv5</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5787,13 +5947,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="Q57" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="R57" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5802,12 +5962,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>20364482</t>
+          <t>1164280530</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20364482</t>
+          <t>https://m.place.naver.com/place/1164280530</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5824,29 +5984,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>맑음체육관 PT 판교역점</t>
+          <t>뱅핏 PT 판교운중점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>malgum_fitness@naver.com</t>
+          <t>bangfit@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1444-1386</t>
+          <t>0507-1345-4609</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 3층 305호</t>
+          <t>경기도 성남시 분당구 운중로 122 골드클래스 8층 801호, 802호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/malgum_fitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5856,20 +6016,24 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40lij</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>X</t>
@@ -5881,13 +6045,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="Q58" t="n">
-        <v>26</v>
+        <v>245</v>
       </c>
       <c r="R58" t="n">
-        <v>105</v>
+        <v>310</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5896,12 +6060,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1424547961</t>
+          <t>1890400282</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1424547961</t>
+          <t>https://m.place.naver.com/place/1890400282</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5918,29 +6082,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>휘트니스클럽S 수내점</t>
+          <t>근육연구소</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>fitnessclubs12@naver.com</t>
+          <t>musclelab_9609@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1311-1188</t>
+          <t>0507-1492-9193</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 11 5층</t>
+          <t>경기도 성남시 분당구 판교역로 109 A동 B212호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/fitnessclubs12</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5950,7 +6114,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5975,13 +6139,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>309</v>
+        <v>5</v>
       </c>
       <c r="Q59" t="n">
-        <v>917</v>
+        <v>172</v>
       </c>
       <c r="R59" t="n">
-        <v>1226</v>
+        <v>177</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5990,12 +6154,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1228787055</t>
+          <t>1655228047</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228787055</t>
+          <t>https://m.place.naver.com/place/1655228047</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6012,29 +6176,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>제로퍼스널트레이닝PT</t>
+          <t>비아핏</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>phh3014@naver.com</t>
+          <t>viafit@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1341-5808</t>
+          <t>0507-1379-7507</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 115 판오션타워 501호</t>
+          <t>경기도 성남시 분당구 판교대장로7길 15-2 지하1층,지상1층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hyunhwa_zero</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6044,7 +6208,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6054,10 +6218,14 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w37pnp4</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
           <t>X</t>
@@ -6069,13 +6237,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="Q60" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="R60" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6084,12 +6252,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>21647284</t>
+          <t>1772663783</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21647284</t>
+          <t>https://m.place.naver.com/place/1772663783</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6106,34 +6274,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>크레이지핏 PT</t>
+          <t>팀제이맥스 피티 서현점</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>krazyfit@naver.com</t>
+          <t>linefit91@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1488-5883</t>
+          <t>031-702-8296</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
+          <t>경기도 성남시 분당구 서현로180번길 13 2층 206호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6143,7 +6311,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6154,7 +6322,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6163,13 +6331,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>535</v>
+        <v>911</v>
       </c>
       <c r="Q61" t="n">
-        <v>1437</v>
+        <v>549</v>
       </c>
       <c r="R61" t="n">
-        <v>1972</v>
+        <v>1460</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6178,12 +6346,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1628554288</t>
+          <t>1639683746</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628554288</t>
+          <t>https://m.place.naver.com/place/1639683746</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6200,34 +6368,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>핏불짐 판교점</t>
+          <t>피티세븐 퍼스널트레이닝</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>fitbullgym@naver.com</t>
+          <t>body2balance@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1430-9683</t>
+          <t>0507-1400-9428</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2 3층 304호</t>
+          <t>경기도 성남시 분당구 황새울로132번길 22-1 1층 102호 피티세븐</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://linktr.ee/fitbullgym</t>
+          <t>http://www.pts7.com</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6237,18 +6405,22 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4bej5</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6257,13 +6429,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>92</v>
+        <v>302</v>
       </c>
       <c r="Q62" t="n">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="R62" t="n">
-        <v>375</v>
+        <v>593</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6272,12 +6444,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>37814535</t>
+          <t>13093618</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37814535</t>
+          <t>https://m.place.naver.com/place/13093618</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6294,29 +6466,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>턴핏PT 판교운중점</t>
+          <t>맑음체육관 PT 판교역점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sungbin00@naver.com</t>
+          <t>malgum_fitness@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>031-698-4246</t>
+          <t>0507-1444-1386</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 131 803호, 804호</t>
+          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 3층 305호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sungbin00</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6326,20 +6498,24 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wt7dwa7</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
           <t>X</t>
@@ -6351,13 +6527,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="Q63" t="n">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="R63" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6366,12 +6542,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1457398870</t>
+          <t>1424547961</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1457398870</t>
+          <t>https://m.place.naver.com/place/1424547961</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6388,34 +6564,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>유앤바디PT 분당수내점</t>
+          <t>에너지플로우짐</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>unbody@naver.com</t>
+          <t>exerscience@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>031-714-4729</t>
+          <t>0507-1346-9129</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 백현로101번길 12 세인프라자 402호</t>
+          <t>경기도 성남시 분당구 판교역로 230 B동 지하1층 B126-1호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/unbody</t>
+          <t>https://energyflowlab.my.canva.site</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6425,7 +6601,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6445,13 +6621,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>118</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>166</v>
+        <v>38</v>
       </c>
       <c r="R64" t="n">
-        <v>284</v>
+        <v>39</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6460,12 +6636,12 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1853394852</t>
+          <t>1846760075</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1853394852</t>
+          <t>https://m.place.naver.com/place/1846760075</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6482,29 +6658,33 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>바디수</t>
+          <t>버핏그라운드 PT 판교</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>lovelygodus@naver.com</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>070-8802-9000</t>
+          <t>0507-1417-1133</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로44번길 15 101호</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>http://www.bodysoo.co.kr/</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6519,7 +6699,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6530,7 +6710,7 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6539,13 +6719,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6554,12 +6734,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>32497004</t>
+          <t>2029680813</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32497004</t>
+          <t>https://m.place.naver.com/place/2029680813</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -6576,29 +6756,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>업투 휘트니스 분당판교점</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
+          <t>uptofitness-@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>0507-1343-8274</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6608,7 +6788,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6618,10 +6798,14 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ijhg</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr">
         <is>
           <t>X</t>
@@ -6633,13 +6817,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>163</v>
+        <v>619</v>
       </c>
       <c r="Q66" t="n">
-        <v>143</v>
+        <v>291</v>
       </c>
       <c r="R66" t="n">
-        <v>306</v>
+        <v>910</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6648,12 +6832,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>1928497638</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/1928497638</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -6712,10 +6896,14 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ty8f</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr">
         <is>
           <t>X</t>
@@ -6730,10 +6918,10 @@
         <v>22</v>
       </c>
       <c r="Q67" t="n">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="R67" t="n">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6764,29 +6952,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>리,무브먼트</t>
+          <t>리조트휘트니스 PT 판교점</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>sujin6735@naver.com</t>
+          <t>resort_5@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1310-5661</t>
+          <t>0507-1438-0677</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 140 메트로골드 203호</t>
+          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/re__movement</t>
+          <t>https://www.instagram.com/resortfitness__pangyo/</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6821,13 +7009,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>242</v>
+        <v>413</v>
       </c>
       <c r="Q68" t="n">
-        <v>246</v>
+        <v>714</v>
       </c>
       <c r="R68" t="n">
-        <v>488</v>
+        <v>1127</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6836,12 +7024,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1149465061</t>
+          <t>35524502</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1149465061</t>
+          <t>https://m.place.naver.com/place/35524502</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -6858,29 +7046,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>판교피트니스센터</t>
+          <t>트친소</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>towershift@naver.com</t>
+          <t>govlrhaehfdl@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1343-5171</t>
+          <t>0507-1349-0679</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로289번길 20 3층 판교피트니스센터</t>
+          <t>경기도 성남시 분당구 판교공원로2길 9 4층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/towershift</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6890,12 +7078,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6906,22 +7094,22 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="R69" t="n">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6930,12 +7118,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1874121479</t>
+          <t>1911382745</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1874121479</t>
+          <t>https://m.place.naver.com/place/1911382745</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -6952,29 +7140,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>좋은습관PTSTUDIO 판교운중</t>
+          <t>엑서사이언스짐</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>goodhabitpg@naver.com</t>
+          <t>exerscience@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0507-1480-0677</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 6층</t>
+          <t>경기도 성남시 분당구 판교역로 240 삼환하이펙스A동 B1층 B117-1호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/goodhabit_pangyo/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6984,7 +7168,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7005,17 +7189,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="Q70" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="R70" t="n">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7024,12 +7208,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1070284726</t>
+          <t>1746641680</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070284726</t>
+          <t>https://m.place.naver.com/place/1746641680</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7046,29 +7230,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>열정PT 판교점</t>
+          <t>좋은습관PTSTUDIO 판교운중</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ptpassion@naver.com</t>
+          <t>goodhabitpg@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1319-7157</t>
+          <t>0507-1480-0677</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로255번길 9-22 우림W-CITY 지하117호</t>
+          <t>경기도 성남시 분당구 운중로 142 6층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ptpassion</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7078,20 +7262,24 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5wyz9</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr">
         <is>
           <t>X</t>
@@ -7103,13 +7291,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>208</v>
+        <v>63</v>
       </c>
       <c r="Q71" t="n">
-        <v>154</v>
+        <v>29</v>
       </c>
       <c r="R71" t="n">
-        <v>362</v>
+        <v>92</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7118,12 +7306,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1614896755</t>
+          <t>1070284726</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1614896755</t>
+          <t>https://m.place.naver.com/place/1070284726</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7140,29 +7328,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>원프로짐PT</t>
+          <t>핏불짐 판교점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>onepro_gym@naver.com</t>
+          <t>fitbullgym@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1304-9363</t>
+          <t>0507-1430-9683</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서판교로 164 훼미리프라자 402호</t>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2 3층 304호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oneprogym_seopangyo</t>
+          <t>https://linktr.ee/fitbullgym</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7177,15 +7365,19 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4eqla</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr">
         <is>
           <t>X</t>
@@ -7197,13 +7389,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="Q72" t="n">
-        <v>35</v>
+        <v>283</v>
       </c>
       <c r="R72" t="n">
-        <v>49</v>
+        <v>375</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7212,12 +7404,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1663447864</t>
+          <t>37814535</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1663447864</t>
+          <t>https://m.place.naver.com/place/37814535</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7234,29 +7426,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>뱅핏 PT 판교운중점</t>
+          <t>솔리드짐 PT 수내점</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>bangfit@naver.com</t>
+          <t>ppapers@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1345-4609</t>
+          <t>0507-1420-7858</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 122 골드클래스 8층 801호, 802호</t>
+          <t>경기도 성남시 분당구 황새울로258번길 10-7 403호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bangfit_official</t>
+          <t>https://www.instagram.com/solid_gym1</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7291,13 +7483,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>65</v>
+        <v>145</v>
       </c>
       <c r="Q73" t="n">
-        <v>245</v>
+        <v>652</v>
       </c>
       <c r="R73" t="n">
-        <v>310</v>
+        <v>797</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7306,12 +7498,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1890400282</t>
+          <t>1205679892</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1890400282</t>
+          <t>https://m.place.naver.com/place/1205679892</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7328,29 +7520,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>리조트휘트니스 PT 판교점</t>
+          <t>건강한 운동 연구소</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>resort_5@naver.com</t>
+          <t>brave082@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1438-0677</t>
+          <t>0507-1347-2906</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+          <t>경기도 성남시 분당구 서판교로44번길 3-14 102호 건강한 운동 연구소</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/resortfitness__pangyo/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7360,7 +7552,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7381,17 +7573,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>413</v>
+        <v>14</v>
       </c>
       <c r="Q74" t="n">
-        <v>714</v>
+        <v>6</v>
       </c>
       <c r="R74" t="n">
-        <v>1127</v>
+        <v>20</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7400,12 +7592,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>35524502</t>
+          <t>1780907875</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35524502</t>
+          <t>https://m.place.naver.com/place/1780907875</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7422,29 +7614,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>팀제이맥스 피티 서현점</t>
+          <t>턴핏PT 판교운중점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>teamjmax_sh@naver.com</t>
+          <t>sungbin00@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>031-702-8296</t>
+          <t>031-698-4246</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 서현로180번길 13 2층 206호</t>
+          <t>경기도 성남시 분당구 운중로 131 803호, 804호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamjmax_sh</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7454,20 +7646,24 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a9c1</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr">
         <is>
           <t>X</t>
@@ -7479,13 +7675,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>911</v>
+        <v>36</v>
       </c>
       <c r="Q75" t="n">
-        <v>549</v>
+        <v>68</v>
       </c>
       <c r="R75" t="n">
-        <v>1460</v>
+        <v>104</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7494,12 +7690,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1639683746</t>
+          <t>1457398870</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1639683746</t>
+          <t>https://m.place.naver.com/place/1457398870</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -7516,29 +7712,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>솔리드짐 PT 수내점</t>
+          <t>153트레이닝</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ppapers@naver.com</t>
+          <t>trainerps@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1420-7858</t>
+          <t>0507-1361-0679</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 황새울로258번길 10-7 403호</t>
+          <t>경기도 성남시 분당구 판교공원로3길 36 202호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/solid_gym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7548,7 +7744,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7564,22 +7760,22 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>145</v>
+        <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>652</v>
+        <v>19</v>
       </c>
       <c r="R76" t="n">
-        <v>797</v>
+        <v>20</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7588,12 +7784,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1205679892</t>
+          <t>1932735845</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1205679892</t>
+          <t>https://m.place.naver.com/place/1932735845</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">

--- a/naver-place-crawler/results_health/판교_헬스장.xlsx
+++ b/naver-place-crawler/results_health/판교_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -718,10 +718,10 @@
         <v>731</v>
       </c>
       <c r="Q3" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="R3" t="n">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -910,10 +910,10 @@
         <v>663</v>
       </c>
       <c r="Q5" t="n">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="R5" t="n">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1127,39 +1127,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>투엑스휘트니스 분당점</t>
+          <t>구스짐 PT 판교점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2xfit@naver.com</t>
+          <t>chlgudrn1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-782-5115</t>
+          <t>0507-1465-9683</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 177 분당인텔리지2 3F</t>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.2xfitness.co.kr/</t>
+          <t>https://www.instagram.com/9s_gym_pangyo/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>431</v>
+        <v>163</v>
       </c>
       <c r="Q8" t="n">
-        <v>28</v>
+        <v>143</v>
       </c>
       <c r="R8" t="n">
-        <v>459</v>
+        <v>306</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>32278618</t>
+          <t>1088776551</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32278618</t>
+          <t>https://m.place.naver.com/place/1088776551</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,34 +1226,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>버핏그라운드 PT 판교</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>0507-1417-1133</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+          <t>https://www.butfitground.com/4steppt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1263,7 +1267,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1274,7 +1278,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1283,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1302,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>2029680813</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/2029680813</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,39 +1324,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H GYM PT GT 판교2호점</t>
+          <t>험블 휘트니스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hgym9408@naver.com</t>
+          <t>humblefitness@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1353-9408</t>
+          <t>031-697-8768</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 233 302호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://hgym.imweb.me</t>
+          <t>https://blog.naver.com/humblefitness</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1377,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>279</v>
+        <v>141</v>
       </c>
       <c r="Q10" t="n">
-        <v>420</v>
+        <v>1437</v>
       </c>
       <c r="R10" t="n">
-        <v>699</v>
+        <v>1578</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,105 +1396,15 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1850894755</t>
+          <t>1134171602</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850894755</t>
+          <t>https://m.place.naver.com/place/1134171602</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>렛미PT&amp;필라테스스튜디오 분당야탑점</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>let_me_pt_official@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 야탑로69번길 21 영진다이비스상가 2층 210호</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/let_me_pt_official</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>49</v>
-      </c>
-      <c r="R11" t="n">
-        <v>129</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1049956503</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1049956503</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/판교_헬스장.xlsx
+++ b/naver-place-crawler/results_health/판교_헬스장.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="Q2" t="n">
         <v>323</v>
       </c>
       <c r="R2" t="n">
-        <v>2863</v>
+        <v>2864</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -910,10 +910,10 @@
         <v>663</v>
       </c>
       <c r="Q5" t="n">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="R5" t="n">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1033,34 +1033,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>원팀짐</t>
+          <t>구스짐 PT 판교점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>oneteamgym-@naver.com</t>
+          <t>chlgudrn1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>031-702-2070</t>
+          <t>0507-1465-9683</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 128 7층 701호</t>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/oneteamgym1</t>
+          <t>https://www.instagram.com/9s_gym_pangyo/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>493</v>
+        <v>163</v>
       </c>
       <c r="Q7" t="n">
-        <v>289</v>
+        <v>143</v>
       </c>
       <c r="R7" t="n">
-        <v>782</v>
+        <v>306</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1973455447</t>
+          <t>1088776551</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973455447</t>
+          <t>https://m.place.naver.com/place/1088776551</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>베스트바디발란스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
+          <t>wjdwktnso@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>0507-1402-7136</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+          <t>https://blog.naver.com/wjdwktnso</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>163</v>
+        <v>54</v>
       </c>
       <c r="Q8" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="R8" t="n">
-        <v>306</v>
+        <v>161</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>36428321</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/36428321</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,33 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>버핏그라운드 PT 판교</t>
+          <t>H GYM PT GT 판교2호점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>hgym9408@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1417-1133</t>
+          <t>0507-1353-9408</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/4steppt</t>
+          <t>https://hgym.imweb.me</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1262,7 +1258,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1278,7 +1274,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1287,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>699</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2029680813</t>
+          <t>1850894755</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029680813</t>
+          <t>https://m.place.naver.com/place/1850894755</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1324,29 +1320,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>험블 휘트니스 PT</t>
+          <t>렛미PT&amp;필라테스스튜디오 분당야탑점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>humblefitness@naver.com</t>
+          <t>let_me_pt_official@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>031-697-8768</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-3 701호</t>
+          <t>경기도 성남시 분당구 야탑로69번길 21 영진다이비스상가 2층 210호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/humblefitness</t>
+          <t>https://blog.naver.com/let_me_pt_official</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="n">
-        <v>1437</v>
+        <v>49</v>
       </c>
       <c r="R10" t="n">
-        <v>1578</v>
+        <v>129</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1134171602</t>
+          <t>1049956503</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1134171602</t>
+          <t>https://m.place.naver.com/place/1049956503</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/판교_헬스장.xlsx
+++ b/naver-place-crawler/results_health/판교_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>클럽 브릭스 판교</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>lulusoul22@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>031-625-5566</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 분당내곡로 131 판교테크원타워 B1 클럽브릭스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,20 +596,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wolfmmb</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2541</v>
+        <v>331</v>
       </c>
       <c r="Q2" t="n">
-        <v>323</v>
+        <v>94</v>
       </c>
       <c r="R2" t="n">
-        <v>2864</v>
+        <v>425</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1141858723</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1141858723</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -663,7 +667,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>spogym_2@naver.com</t>
+          <t>spogym7@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -680,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spogym_pg</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wpasubw</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -740,45 +748,41 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>healthboygym78@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,23 +792,27 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wi2wapb</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1765</v>
+        <v>2543</v>
       </c>
       <c r="Q4" t="n">
-        <v>250</v>
+        <v>323</v>
       </c>
       <c r="R4" t="n">
-        <v>2015</v>
+        <v>2866</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -850,39 +858,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헤일로짐24시 헬스 PT 판교점</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>halogym02@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1315-8840</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/933331</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -892,10 +904,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42raj</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>O</t>
@@ -903,17 +919,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>663</v>
+        <v>1765</v>
       </c>
       <c r="Q5" t="n">
-        <v>933</v>
+        <v>250</v>
       </c>
       <c r="R5" t="n">
-        <v>1596</v>
+        <v>2015</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +938,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1806695299</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806695299</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -944,29 +960,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포짐 판교역점</t>
+          <t>헤일로짐24시 헬스 PT 판교점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>showmethecash@naver.com</t>
+          <t>halogym02@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1436-1236</t>
+          <t>0507-1315-8840</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 117 B101호</t>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spogym_p.g/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -976,7 +992,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -986,28 +1002,32 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcfevb4</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1253</v>
+        <v>663</v>
       </c>
       <c r="Q6" t="n">
-        <v>641</v>
+        <v>933</v>
       </c>
       <c r="R6" t="n">
-        <v>1894</v>
+        <v>1596</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,51 +1036,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1088507385</t>
+          <t>1806695299</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088507385</t>
+          <t>https://m.place.naver.com/place/1806695299</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>스포짐 판교역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
+          <t>showmethecash@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>0507-1436-1236</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 분당내곡로 117 B101호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1070,7 +1090,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1080,10 +1100,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w444pd</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>163</v>
+        <v>1253</v>
       </c>
       <c r="Q7" t="n">
-        <v>143</v>
+        <v>641</v>
       </c>
       <c r="R7" t="n">
-        <v>306</v>
+        <v>1894</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,56 +1134,60 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>1088507385</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/1088507385</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>베스트바디발란스</t>
+          <t>버핏그라운드 판교벤처타운</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>wjdwktnso@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1402-7136</t>
+          <t>0507-1315-3624</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
+          <t>경기도 성남시 분당구 대왕판교로644번길 49 B2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjdwktnso</t>
+          <t>https://www.butfitground.com/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1174,28 +1202,32 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzq100p</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="Q8" t="n">
-        <v>107</v>
+        <v>29</v>
       </c>
       <c r="R8" t="n">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,17 +1236,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36428321</t>
+          <t>2064425838</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36428321</t>
+          <t>https://m.place.naver.com/place/2064425838</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1226,34 +1258,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H GYM PT GT 판교2호점</t>
+          <t>구스짐 PT 판교점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hgym9408@naver.com</t>
+          <t>chlgudrn1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1353-9408</t>
+          <t>0507-1465-9683</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 233 302호</t>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://hgym.imweb.me</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1263,15 +1295,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyuehl2</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1319,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>279</v>
+        <v>164</v>
       </c>
       <c r="Q9" t="n">
-        <v>420</v>
+        <v>143</v>
       </c>
       <c r="R9" t="n">
-        <v>699</v>
+        <v>307</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,17 +1334,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1850894755</t>
+          <t>1088776551</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1850894755</t>
+          <t>https://m.place.naver.com/place/1088776551</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1320,25 +1356,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>렛미PT&amp;필라테스스튜디오 분당야탑점</t>
+          <t>쿼드짐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>let_me_pt_official@naver.com</t>
+          <t>quadgym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1303-9415</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 야탑로69번길 21 영진다이비스상가 2층 210호</t>
+          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/let_me_pt_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,20 +1388,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc5w2o</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1417,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q10" t="n">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="R10" t="n">
-        <v>129</v>
+        <v>184</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1432,209 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1049956503</t>
+          <t>1759307500</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1049956503</t>
+          <t>https://m.place.naver.com/place/1759307500</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H GYM PT GT 판교2호점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>hgym9408@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1353-9408</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://hgym.imweb.me</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47alh</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>279</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>421</v>
+      </c>
+      <c r="R11" t="n">
+        <v>700</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1850894755</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1850894755</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>머슬짐 PT 분당서현점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>musclegym_@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1436-9680</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로342번길 19 유성그린빌딩 6층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/musclegym_</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>367</v>
+      </c>
+      <c r="R12" t="n">
+        <v>567</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1208748555</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1208748555</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/판교_헬스장.xlsx
+++ b/naver-place-crawler/results_health/판교_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>클럽 브릭스 판교</t>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lulusoul22@naver.com</t>
+          <t>healthboygym78@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>031-625-5566</t>
+          <t>0507-1402-1275</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 131 판교테크원타워 B1 클럽브릭스</t>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,24 +596,20 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wolfmmb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>331</v>
+        <v>2543</v>
       </c>
       <c r="Q2" t="n">
-        <v>94</v>
+        <v>323</v>
       </c>
       <c r="R2" t="n">
-        <v>425</v>
+        <v>2866</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1141858723</t>
+          <t>1835201778</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1141858723</t>
+          <t>https://m.place.naver.com/place/1835201778</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -667,7 +663,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>spogym7@naver.com</t>
+          <t>spogym_2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -684,7 +680,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/spogym_pg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wpasubw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -755,34 +747,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>버핏그라운드 판교</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>partner@butfitseoul.com</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1329-4325</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pt.butfitground.com/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,27 +788,23 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wi2wapb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2543</v>
+        <v>1766</v>
       </c>
       <c r="Q4" t="n">
-        <v>323</v>
+        <v>250</v>
       </c>
       <c r="R4" t="n">
-        <v>2866</v>
+        <v>2016</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1136752576</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1136752576</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,43 +850,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>헤일로짐24시 헬스 PT 판교점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>halogym02@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1315-8840</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://booking.naver.com/booking/6/bizes/933331</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -904,14 +892,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42raj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>O</t>
@@ -919,17 +903,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1765</v>
+        <v>663</v>
       </c>
       <c r="Q5" t="n">
-        <v>250</v>
+        <v>934</v>
       </c>
       <c r="R5" t="n">
-        <v>2015</v>
+        <v>1597</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -938,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1806695299</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1806695299</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -960,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헤일로짐24시 헬스 PT 판교점</t>
+          <t>스포짐 판교역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>halogym02@naver.com</t>
+          <t>showmethecash@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1315-8840</t>
+          <t>0507-1436-1236</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+          <t>경기도 성남시 분당구 분당내곡로 117 B101호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/spogym_p.g/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -992,7 +976,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1002,32 +986,28 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcfevb4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>663</v>
+        <v>1253</v>
       </c>
       <c r="Q6" t="n">
-        <v>933</v>
+        <v>641</v>
       </c>
       <c r="R6" t="n">
-        <v>1596</v>
+        <v>1894</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1036,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1806695299</t>
+          <t>1088507385</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806695299</t>
+          <t>https://m.place.naver.com/place/1088507385</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1058,56 +1038,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>스포짐 판교역점</t>
+          <t>투엑스휘트니스 분당점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>showmethecash@naver.com</t>
+          <t>2xfit@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1436-1236</t>
+          <t>031-782-5115</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 117 B101호</t>
+          <t>경기도 성남시 분당구 정자일로 177 분당인텔리지2 3F</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.2xfitness.co.kr/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w444pd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1119,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1253</v>
+        <v>431</v>
       </c>
       <c r="Q7" t="n">
-        <v>641</v>
+        <v>28</v>
       </c>
       <c r="R7" t="n">
-        <v>1894</v>
+        <v>459</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1134,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1088507385</t>
+          <t>32278618</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088507385</t>
+          <t>https://m.place.naver.com/place/32278618</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1151,43 +1127,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교벤처타운</t>
+          <t>구스짐 PT 판교점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>butfitseoul@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>chlgudrn1@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1315-3624</t>
+          <t>0507-1465-9683</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로644번길 49 B2층</t>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.butfitground.com/</t>
+          <t>https://www.instagram.com/9s_gym_pangyo/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1197,22 +1169,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wzq100p</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1221,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="Q8" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="R8" t="n">
-        <v>140</v>
+        <v>308</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1236,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2064425838</t>
+          <t>1088776551</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064425838</t>
+          <t>https://m.place.naver.com/place/1088776551</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1258,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>쿼드짐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
+          <t>quadgym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>0507-1303-9415</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/quadgym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1290,24 +1258,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wyuehl2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1319,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="Q9" t="n">
-        <v>143</v>
+        <v>102</v>
       </c>
       <c r="R9" t="n">
-        <v>307</v>
+        <v>184</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1334,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>1759307500</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/1759307500</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1356,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>쿼드짐</t>
+          <t>베스트바디발란스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>quadgym@naver.com</t>
+          <t>wjdwktnso@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1303-9415</t>
+          <t>0507-1402-7136</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
+          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/wjdwktnso</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1388,24 +1352,20 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc5w2o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1413,17 +1373,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="Q10" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="R10" t="n">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1432,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1759307500</t>
+          <t>36428321</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759307500</t>
+          <t>https://m.place.naver.com/place/36428321</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1496,14 +1456,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w47alh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1518,10 +1474,10 @@
         <v>279</v>
       </c>
       <c r="Q11" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="R11" t="n">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1539,100 +1495,6 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>머슬짐 PT 분당서현점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>musclegym_@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1436-9680</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기도 성남시 분당구 황새울로342번길 19 유성그린빌딩 6층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/musclegym_</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>367</v>
-      </c>
-      <c r="R12" t="n">
-        <v>567</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1208748555</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1208748555</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/판교_헬스장.xlsx
+++ b/naver-place-crawler/results_health/판교_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>헬스보이짐 헬스 PT 판교역점</t>
+          <t>업투휘트니스 분당삼평점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>healthboygym78@naver.com</t>
+          <t>upto_sampyeong@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1402-1275</t>
+          <t>0507-1466-1103</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+          <t>경기도 성남시 분당구 판교로 375 4층 401-2,402~405호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+          <t>https://blog.naver.com/upto_sampyeong</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2543</v>
+        <v>563</v>
       </c>
       <c r="Q2" t="n">
-        <v>323</v>
+        <v>570</v>
       </c>
       <c r="R2" t="n">
-        <v>2866</v>
+        <v>1133</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1835201778</t>
+          <t>1878300058</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1835201778</t>
+          <t>https://m.place.naver.com/place/1878300058</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>스포짐 판교점</t>
+          <t>트랜스핏짐 서현역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>spogym_2@naver.com</t>
+          <t>transfit_gym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1476-8384</t>
+          <t>0507-1387-9682</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
+          <t>경기도 성남시 분당구 분당로53번길 15 지하1층 트랜스핏짐 서현역점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spogym_pg</t>
+          <t>https://blog.naver.com/transfit_gym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>731</v>
+        <v>2191</v>
       </c>
       <c r="Q3" t="n">
-        <v>624</v>
+        <v>2253</v>
       </c>
       <c r="R3" t="n">
-        <v>1355</v>
+        <v>4444</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>20123697</t>
+          <t>1487183442</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20123697</t>
+          <t>https://m.place.naver.com/place/1487183442</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -752,33 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>버핏그라운드 판교</t>
+          <t>밥스짐 분당점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>butfitground@naver.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>partner@butfitseoul.com</t>
-        </is>
-      </c>
+          <t>somng96@naver.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1329-4325</t>
+          <t>0507-1474-7017</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+          <t>경기도 성남시 분당구 성남대로 449 로얄팰리스 에이동 212, 213, 214호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://pt.butfitground.com/</t>
+          <t>https://www.instagram.com/bobsgymbob/profilecard/?igsh=MTFxcDRvanRsZ2ZyNA==</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -804,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1766</v>
+        <v>82</v>
       </c>
       <c r="Q4" t="n">
-        <v>250</v>
+        <v>185</v>
       </c>
       <c r="R4" t="n">
-        <v>2016</v>
+        <v>267</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1136752576</t>
+          <t>1581057750</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1136752576</t>
+          <t>https://m.place.naver.com/place/1581057750</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -850,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헤일로짐24시 헬스 PT 판교점</t>
+          <t>F45 판교</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>halogym02@naver.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1315-8840</t>
-        </is>
-      </c>
+          <t>ksh1992001@naver.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>pangyo.admin@f45training.kr</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하 1층 119-6호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/933331</t>
+          <t>http://www.f45training.kr/pangyo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -887,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -898,22 +894,22 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>663</v>
+        <v>103</v>
       </c>
       <c r="Q5" t="n">
-        <v>934</v>
+        <v>105</v>
       </c>
       <c r="R5" t="n">
-        <v>1597</v>
+        <v>208</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1806695299</t>
+          <t>1017940051</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806695299</t>
+          <t>https://m.place.naver.com/place/1017940051</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -944,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스포짐 판교역점</t>
+          <t>커스텀핏 PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>showmethecash@naver.com</t>
+          <t>customfitpt@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1436-1236</t>
+          <t>031-8016-5677</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 분당내곡로 117 B101호</t>
+          <t>경기도 성남시 분당구 운중로 123 마크시티 오렌지동 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/spogym_p.g/</t>
+          <t>https://booking.naver.com/https://booking.naver.com/booking/5/bizes/795160/items/4714422?preview=1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -997,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1253</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>641</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1894</v>
+        <v>5</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1088507385</t>
+          <t>35644006</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088507385</t>
+          <t>https://m.place.naver.com/place/35644006</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1038,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>투엑스휘트니스 분당점</t>
+          <t>원팀짐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2xfit@naver.com</t>
+          <t>oneteamgym-@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>031-782-5115</t>
+          <t>031-702-2070</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 177 분당인텔리지2 3F</t>
+          <t>경기도 성남시 분당구 운중로 128 7층 701호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.2xfitness.co.kr/</t>
+          <t>https://www.instagram.com/oneteamgym1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1075,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1095,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>431</v>
+        <v>493</v>
       </c>
       <c r="Q7" t="n">
-        <v>28</v>
+        <v>291</v>
       </c>
       <c r="R7" t="n">
-        <v>459</v>
+        <v>784</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>32278618</t>
+          <t>1973455447</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32278618</t>
+          <t>https://m.place.naver.com/place/1973455447</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1132,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>구스짐 PT 판교점</t>
+          <t>하이퀄짐 헬스PT 판교점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chlgudrn1@naver.com</t>
+          <t>highqualgym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1465-9683</t>
+          <t>0507-1364-9601</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+          <t>경기도 성남시 분당구 운중로 128 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+          <t>https://www.instagram.com/highqualgym2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="Q8" t="n">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="R8" t="n">
-        <v>308</v>
+        <v>161</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,51 +1200,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1088776551</t>
+          <t>1012638231</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088776551</t>
+          <t>https://m.place.naver.com/place/1012638231</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>쿼드짐</t>
+          <t>그라운드피트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>quadgym@naver.com</t>
+          <t>ground-fitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1303-9415</t>
+          <t>0507-1464-5758</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 정자일로 121 더샵스타파크 상가1층 b-18호</t>
+          <t>경기도 성남시 분당구 서현로 170 풍림아이원플러스 3층 301호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/quadgym</t>
+          <t>https://blog.naver.com/ground-fitness</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>82</v>
+        <v>374</v>
       </c>
       <c r="Q9" t="n">
-        <v>102</v>
+        <v>1219</v>
       </c>
       <c r="R9" t="n">
-        <v>184</v>
+        <v>1593</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,51 +1294,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1759307500</t>
+          <t>1472483345</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1759307500</t>
+          <t>https://m.place.naver.com/place/1472483345</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>베스트바디발란스</t>
+          <t>클럽 브릭스 판교</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wjdwktnso@naver.com</t>
+          <t>club_breex@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1402-7136</t>
+          <t>031-625-5566</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 성남대로331번길 3-9 백궁프라자 3차 202호</t>
+          <t>경기도 성남시 분당구 분당내곡로 131 판교테크원타워 B1 클럽브릭스</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wjdwktnso</t>
+          <t>https://blog.naver.com/club_breex</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>54</v>
+        <v>331</v>
       </c>
       <c r="Q10" t="n">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="R10" t="n">
-        <v>161</v>
+        <v>425</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,61 +1388,61 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>36428321</t>
+          <t>1141858723</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36428321</t>
+          <t>https://m.place.naver.com/place/1141858723</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H GYM PT GT 판교2호점</t>
+          <t>휘트니스클럽S 이매점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hgym9408@naver.com</t>
+          <t>fitnessclubs10@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1353-9408</t>
+          <t>0507-1442-7786</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 성남시 분당구 운중로 233 302호</t>
+          <t>경기도 성남시 분당구 판교로 446 그린프라자 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://hgym.imweb.me</t>
+          <t>https://blog.naver.com/fitnessclubs10</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1471,32 +1467,6146 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>199</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>525</v>
+      </c>
+      <c r="R11" t="n">
+        <v>724</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>38673070</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38673070</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>스포짐 판교역점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>showmethecash@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1436-1236</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 분당내곡로 117 B101호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/spogym_p.g/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1253</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>642</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1895</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1088507385</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1088507385</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>바디센서리 판교점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>bodysensory@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1344-2096</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 41 프라임스퀘어 10층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/BumGi</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>292</v>
+      </c>
+      <c r="R13" t="n">
+        <v>338</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1786901360</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1786901360</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>피트니스패밀리</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>tkdkrkwl@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>031-739-7188</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로712번길 22</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>30817753</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/30817753</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>파크뷰휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>parkviewf1004@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>parkview.f.1004@gmail.com</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>031-783-3000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로 248 파크뷰상가 3층</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.parkviewfc.co.kr</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>127</v>
+      </c>
+      <c r="R15" t="n">
+        <v>175</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>11847077</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11847077</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>런던피트니스&amp;필라테스 분당이매점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>londoner83@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1406-9679</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 성남대로779번길 13 오성프라자빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/londoner83</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>1342</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>473</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1815</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>13530251</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13530251</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>스타디온 판교 크로스핏</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>sbkim10@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>031-603-1109</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로177번길 25 지하B103호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/stadion_pangyo_crossfit?igsh=MXg2azI4ZjFsemtkMw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>326</v>
+      </c>
+      <c r="R17" t="n">
+        <v>440</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1332230479</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1332230479</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>크로스핏 라운지</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>crossfit_lounge@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1321-6851</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로319번길 8-4 지하1층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/crossfit_lounge</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>271</v>
+      </c>
+      <c r="R18" t="n">
+        <v>314</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2067270233</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2067270233</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>엔엘휘트니스 분당이매점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>nlfitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1415-2075</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 440 지하1층</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nlfitness2_imae/</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>643</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>241</v>
+      </c>
+      <c r="R19" t="n">
+        <v>884</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1194690742</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1194690742</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>익스홀릭 가넷 이매점</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>exholicimae@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1450-3374</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 이매로 45 이수프라자</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/exholicimae</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>310</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>228</v>
+      </c>
+      <c r="R20" t="n">
+        <v>538</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>21281338</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21281338</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>헬스보이짐&amp;필라걸 수내점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>healthboy40@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1380-2239</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 내정로173번길 49 5층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/healthboy40/223688037867</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>967</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>737</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1704</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1973151166</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1973151166</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>스포애니 서현역점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>spoany22@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>031-706-8522</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로 324 좋은상호저축은행빌딩 B1층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spoany22</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>954</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2039</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2993</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>13025013</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13025013</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>짐라이언피트니스 수내역1호점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>liongym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1319-1102</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 수내로46번길 11 지하1층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gymlion_sunae</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>1706</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>345</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2051</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1628575924</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1628575924</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>버핏그라운드 판교벤처타운</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1315-3624</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로644번길 49 B2층</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.butfitground.com/</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>29</v>
+      </c>
+      <c r="R24" t="n">
+        <v>140</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2064425838</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2064425838</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>스포짐 판교점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>spogym_2@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1476-8384</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로 670 유스페이스2 B동 지하1층</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/spogym_pg</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>731</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>624</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1355</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>20123697</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20123697</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>헬스플러스 판교5호점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>healthplus_pangyo5@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1313-1507</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로2길 2 지하1층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/healthplus_pangyo5/</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>679</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1078</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1757</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1086359388</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1086359388</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>고릴라멀티짐 분당서현점</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>gorillagym6@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1373-0880</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로 192 야베스벨리 5층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gorillamultigym_bundangseohyun?igsh=cWMyMDFqYjZsdjg5&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>652</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>949</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1601</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>31457116</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31457116</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>봇들마을8단지한신휴플러스아파트휘트니스센터</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1logdesign@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 153</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1443133117</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1443133117</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>헤일로짐24시 헬스 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>halogym02@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1315-8840</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로 660 유스페이스1 지하1층 127호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/6/bizes/933331</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>663</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>934</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1597</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1806695299</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1806695299</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>레조나헬스랩PT 서판교점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>resonar_healthlab@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1411-1104</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로2길 9 4층 레조나헬스랩PT 서판교점</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/resonar_healthlab</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>202</v>
+      </c>
+      <c r="R30" t="n">
+        <v>258</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1644348689</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1644348689</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>운동공간픽스앤빌드</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>physio_congmi@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>themosttimes@tmt.co.kr</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1433-4667</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 산운로160번길 10 1층 101호</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.themosttimes.co.kr/39064</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>432</v>
+      </c>
+      <c r="R31" t="n">
+        <v>496</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1637759423</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1637759423</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>F45 서현</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ssun_mom@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>031-702-4520</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로342번길 21 대정빌딩 지하 1층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/f45_seohyeon/</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>468</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>96</v>
+      </c>
+      <c r="R32" t="n">
+        <v>564</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1316630678</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1316630678</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PDC스포츠센터</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>spxkzjs12@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>031-8060-0377</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 242 판교디지털센터 A동 2층 PDC스포츠센터</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>19</v>
+      </c>
+      <c r="R33" t="n">
+        <v>71</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1057141943</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1057141943</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>산운휘트니스센타</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>hak0234@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1405-9688</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교원로 68</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>20123481</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20123481</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>팀버핏 판교</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 힐스테이트판교역 지하3층 B3008</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/butfitground</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>95</v>
+      </c>
+      <c r="R35" t="n">
+        <v>331</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1004612269</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1004612269</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>버핏그라운드 판교</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1329-4325</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 B3007</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://pt.butfitground.com/</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>1766</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>250</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2016</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1136752576</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1136752576</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>헬스보이짐 헬스 PT 판교역점</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>healthboygym78@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1402-1275</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 58 지하1층</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/healthboygym78/223380215625</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>2545</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>323</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2868</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1835201778</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1835201778</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>블랙스미스짐 헬스PT 판교점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>emmaholic1@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1352-4388</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 지하2층 비2147호, 비2148호</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>http://blacksmithgym.kr/</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>195</v>
+      </c>
+      <c r="R38" t="n">
+        <v>302</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1462760829</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1462760829</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>뱅핏 PT 판교운중점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>bangfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1345-4609</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 122 골드클래스 8층 801호, 802호</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bangfit_official</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>245</v>
+      </c>
+      <c r="R39" t="n">
+        <v>310</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1890400282</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1890400282</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>153트레이닝</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>trainerps@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1361-0679</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교공원로3길 36 202호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/everyworkout/products/5462434513</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>19</v>
+      </c>
+      <c r="R40" t="n">
+        <v>20</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1932735845</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1932735845</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>여성전용 비조 필라PT 자이로토닉</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>viyulgallery@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>themosttimes@tmt.co.kr</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 132</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.themosttimes.co.kr/43811</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>50</v>
+      </c>
+      <c r="R41" t="n">
+        <v>179</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1600591794</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1600591794</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>유앤바디PT 분당수내점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>unbody@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>031-714-4729</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 백현로101번길 12 세인프라자 402호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/unbody</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>169</v>
+      </c>
+      <c r="R42" t="n">
+        <v>287</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1853394852</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1853394852</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>린바디핏 PT 판교본점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>leanbodyfitv2@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1302-8312</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로 670 지하113호</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/leanbodyfitv2</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>108</v>
+      </c>
+      <c r="R43" t="n">
+        <v>243</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1699238533</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1699238533</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>솔리드짐 PT 수내점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ppapers@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1420-7858</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로258번길 10-7 403호</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/solid_gym1</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>652</v>
+      </c>
+      <c r="R44" t="n">
+        <v>797</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1205679892</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1205679892</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>이상해GYM PT 판교역점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>isanghaegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1399-9644</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 지2층 B2086호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@isanghaegym100?si=1UMNdVN5UY8yHcHo</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>124</v>
+      </c>
+      <c r="R45" t="n">
+        <v>191</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1053530808</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1053530808</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>포랩 이즈메디운동센터</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>for_lab2017@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1432-1575</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로 192 야베스밸리 9층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/for_lab2017</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>289</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>158</v>
+      </c>
+      <c r="R46" t="n">
+        <v>447</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>917204514</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/917204514</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>피티스튜디오이룸 PT EROOM</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ptstudioeroom@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1361-7934</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 대왕판교로606번길 45 3층 303호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ptstudioeroom</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>32</v>
+      </c>
+      <c r="R47" t="n">
+        <v>79</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1164280530</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1164280530</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>핏앤클래시 PT</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>fitclassy22@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1325-5251</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서판교로 154 낙생빌딩 201호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitclassy22</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>22</v>
+      </c>
+      <c r="R48" t="n">
+        <v>65</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1283224823</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1283224823</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>핏불짐 판교점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>fitbullgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1430-9683</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 61 자유퍼스트프라자2 3층 304호</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/fitbullgym</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>284</v>
+      </c>
+      <c r="R49" t="n">
+        <v>376</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>37814535</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37814535</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>바디수</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>lovelygodus@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>070-8802-9000</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서판교로44번길 15 101호</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>http://www.bodysoo.co.kr/</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>11</v>
+      </c>
+      <c r="R50" t="n">
+        <v>16</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>32497004</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32497004</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>H GYM PT 대장3호점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>hgym03@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1329-9408</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교대장로 84 304호</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://hgym.co.kr</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>111</v>
+      </c>
+      <c r="R51" t="n">
+        <v>222</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1027491629</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1027491629</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>판교피트니스센터</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>towershift@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1343-5171</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로289번길 20 3층 판교피트니스센터</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/towershift</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>13</v>
+      </c>
+      <c r="R52" t="n">
+        <v>21</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1874121479</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1874121479</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>제로퍼스널트레이닝PT</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>phh3014@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1341-5808</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 115 판오션타워 501호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hyunhwa_zero</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>10</v>
+      </c>
+      <c r="R53" t="n">
+        <v>15</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>21647284</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21647284</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>구스짐 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>chlgudrn1@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1465-9683</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 374 스타식스코아2 3층</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/9s_gym_pangyo/</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>165</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>144</v>
+      </c>
+      <c r="R54" t="n">
+        <v>309</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1088776551</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1088776551</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>피티세븐 퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>body2balance@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1400-9428</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 황새울로132번길 22-1 1층 102호 피티세븐</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>http://www.pts7.com</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>302</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>290</v>
+      </c>
+      <c r="R55" t="n">
+        <v>592</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>13093618</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13093618</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>휘트니스클럽S 수내점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>fitnessclubs12@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1311-1188</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 백현로101번길 11 5층</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/fitnessclubs12</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>308</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>917</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1225</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1228787055</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1228787055</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>열정PT 판교점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ptpassion@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1319-7157</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로255번길 9-22 우림W-CITY 지하117호</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ptpassion</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>207</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>154</v>
+      </c>
+      <c r="R57" t="n">
+        <v>361</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1614896755</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1614896755</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>맑음체육관 PT 판교역점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>malgum_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1444-1386</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로192번길 22 효성해링턴타워 3층 305호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/malgum_fitness</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>26</v>
+      </c>
+      <c r="R58" t="n">
+        <v>105</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1424547961</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1424547961</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>H GYM PT GT 판교2호점</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>hgym9408@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1353-9408</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 233 302호</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://hgym.imweb.me</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
         <v>279</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q59" t="n">
         <v>422</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R59" t="n">
         <v>701</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
         <is>
           <t>1850894755</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1850894755</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>팀제이맥스 피티 서현점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>teamjmax_sh@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>031-702-8296</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서현로180번길 13 2층 206호</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/teamjmax_sh</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>910</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>548</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1458</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1639683746</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1639683746</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>엑서사이언스짐</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>exerscience@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 240 삼환하이펙스A동 B1층 B117-1호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>143</v>
+      </c>
+      <c r="R61" t="n">
+        <v>150</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1746641680</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1746641680</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>원프로짐PT</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>onepro_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1304-9363</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서판교로 164 훼미리프라자 402호</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oneprogym_seopangyo</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>37</v>
+      </c>
+      <c r="R62" t="n">
+        <v>51</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1663447864</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1663447864</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>스윗바디</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>superfly3@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>031-701-4327</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로2번길 36 1층 스윗바디</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/superfly3</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>19</v>
+      </c>
+      <c r="R63" t="n">
+        <v>82</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>20364482</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20364482</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>에너지플로우짐</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>exerscience@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1346-9129</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 230 B동 지하1층 B126-1호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://energyflowlab.my.canva.site</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>38</v>
+      </c>
+      <c r="R64" t="n">
+        <v>39</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1846760075</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1846760075</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>버핏그라운드 PT 판교</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>butfitground@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>butfitseoul@butfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1417-1133</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 136 B3007호</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://www.butfitground.com/4steppt</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2029680813</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2029680813</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>리,무브먼트</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>sujin6735@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1310-5661</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 140 메트로골드 203호</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/re__movement</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>242</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>246</v>
+      </c>
+      <c r="R66" t="n">
+        <v>488</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1149465061</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1149465061</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>비아핏</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>viafit@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1379-7507</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교대장로7길 15-2 지하1층,지상1층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viafit_no.1</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>24</v>
+      </c>
+      <c r="R67" t="n">
+        <v>50</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1772663783</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1772663783</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>크레이지핏 PT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>krazyfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1488-5883</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 정자일로198번길 6-5 3층 크레이지핏</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://m.booking.naver.com/booking/13/bizes/205740?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>539</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1438</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1977</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1628554288</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1628554288</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>업투 휘트니스 분당판교점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>uptofitness-@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1343-8274</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 59 6층 601-605호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/uptofitness-</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>622</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>291</v>
+      </c>
+      <c r="R69" t="n">
+        <v>913</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1928497638</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1928497638</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>근육연구소</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>musclelab_9609@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1492-9193</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로 109 A동 B212호</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/musclelab_9609</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>172</v>
+      </c>
+      <c r="R70" t="n">
+        <v>177</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1655228047</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1655228047</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>턴핏PT 판교운중점</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>sungbin00@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>031-698-4246</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 131 803호, 804호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sungbin00</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>68</v>
+      </c>
+      <c r="R71" t="n">
+        <v>104</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1457398870</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1457398870</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>건강한 운동 연구소</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>brave082@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1347-2906</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 서판교로44번길 3-14 102호 건강한 운동 연구소</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>6</v>
+      </c>
+      <c r="R72" t="n">
+        <v>20</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1780907875</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1780907875</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>좋은습관PTSTUDIO 판교운중</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>goodhabitpg@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1480-0677</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 142 6층</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/goodhabit_pangyo/</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>30</v>
+      </c>
+      <c r="R73" t="n">
+        <v>93</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1070284726</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1070284726</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>리조트휘트니스 PT 판교점</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>resort_5@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1438-0677</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 운중로 142 판교메디칼타워 6층, 7층</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/resortfitness__pangyo/</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>413</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>715</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1128</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>35524502</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35524502</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>바로선운동센터 판교점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>coolksh11@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 동판교로 61 2층 201호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/coolksh11</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>189</v>
+      </c>
+      <c r="R75" t="n">
+        <v>211</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2015061102</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2015061102</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>데스런 판교점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>deslun@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1412-6347</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교역로2번길 38</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>http://www.deslun.co.kr</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>437</v>
+      </c>
+      <c r="R76" t="n">
+        <v>459</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>31469573</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31469573</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
